--- a/research/traditional_assets/database/data/brazil/brazil_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_packaging_container.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09313787277854819</v>
+        <v>0.09285090401110112</v>
       </c>
       <c r="C2">
-        <v>506.8548518138904</v>
+        <v>503.6899496511459</v>
       </c>
       <c r="D2">
-        <v>413.3548518138904</v>
+        <v>415.8759496511458</v>
       </c>
       <c r="E2">
-        <v>-308.4</v>
+        <v>-302.714</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.685999999999999</v>
       </c>
       <c r="G2">
         <v>93.5</v>
@@ -1445,28 +1445,28 @@
         <v>101.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2860057999999999</v>
       </c>
       <c r="N2">
-        <v>101.9</v>
+        <v>101.6139942</v>
       </c>
       <c r="O2">
-        <v>34.646</v>
+        <v>34.548758028</v>
       </c>
       <c r="P2">
-        <v>67.25399999999999</v>
+        <v>67.065236172</v>
       </c>
       <c r="Q2">
-        <v>93.354</v>
+        <v>93.16523617200001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09313787277854819</v>
+        <v>0.09345345859707184</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6210843142787699</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>356.2864809035342</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09285090401110112</v>
+        <v>0.09256393524365407</v>
       </c>
       <c r="C3">
-        <v>503.6899496511459</v>
+        <v>500.5559891247369</v>
       </c>
       <c r="D3">
-        <v>415.8759496511458</v>
+        <v>418.4279891247369</v>
       </c>
       <c r="E3">
-        <v>-302.714</v>
+        <v>-297.028</v>
       </c>
       <c r="F3">
-        <v>5.685999999999999</v>
+        <v>11.372</v>
       </c>
       <c r="G3">
         <v>93.5</v>
@@ -1527,28 +1527,28 @@
         <v>101.9</v>
       </c>
       <c r="M3">
-        <v>0.2860057999999999</v>
+        <v>0.5720115999999998</v>
       </c>
       <c r="N3">
-        <v>101.6139942</v>
+        <v>101.3279884</v>
       </c>
       <c r="O3">
-        <v>34.548758028</v>
+        <v>34.451516056</v>
       </c>
       <c r="P3">
-        <v>67.065236172</v>
+        <v>66.87647234399999</v>
       </c>
       <c r="Q3">
-        <v>93.16523617200001</v>
+        <v>92.976472344</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09345345859707184</v>
+        <v>0.09377548494250415</v>
       </c>
       <c r="T3">
-        <v>0.6210843142787699</v>
+        <v>0.6252813970891414</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>356.2864809035342</v>
+        <v>178.1432404517671</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09256393524365407</v>
+        <v>0.09227696647620701</v>
       </c>
       <c r="C4">
-        <v>500.5559891247369</v>
+        <v>497.4535433755495</v>
       </c>
       <c r="D4">
-        <v>418.4279891247369</v>
+        <v>421.0115433755495</v>
       </c>
       <c r="E4">
-        <v>-297.028</v>
+        <v>-291.342</v>
       </c>
       <c r="F4">
-        <v>11.372</v>
+        <v>17.058</v>
       </c>
       <c r="G4">
         <v>93.5</v>
@@ -1609,28 +1609,28 @@
         <v>101.9</v>
       </c>
       <c r="M4">
-        <v>0.5720115999999998</v>
+        <v>0.8580173999999998</v>
       </c>
       <c r="N4">
-        <v>101.3279884</v>
+        <v>101.0419826</v>
       </c>
       <c r="O4">
-        <v>34.451516056</v>
+        <v>34.354274084</v>
       </c>
       <c r="P4">
-        <v>66.87647234399999</v>
+        <v>66.68770851599999</v>
       </c>
       <c r="Q4">
-        <v>92.976472344</v>
+        <v>92.787708516</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09377548494250415</v>
+        <v>0.09410415100639898</v>
       </c>
       <c r="T4">
-        <v>0.6252813970891414</v>
+        <v>0.6295650176894175</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>178.1432404517671</v>
+        <v>118.7621603011781</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09227696647620701</v>
+        <v>0.09198999770875994</v>
       </c>
       <c r="C5">
-        <v>497.4535433755495</v>
+        <v>494.3831997876857</v>
       </c>
       <c r="D5">
-        <v>421.0115433755495</v>
+        <v>423.6271997876856</v>
       </c>
       <c r="E5">
-        <v>-291.342</v>
+        <v>-285.656</v>
       </c>
       <c r="F5">
-        <v>17.058</v>
+        <v>22.744</v>
       </c>
       <c r="G5">
         <v>93.5</v>
@@ -1691,28 +1691,28 @@
         <v>101.9</v>
       </c>
       <c r="M5">
-        <v>0.8580173999999998</v>
+        <v>1.1440232</v>
       </c>
       <c r="N5">
-        <v>101.0419826</v>
+        <v>100.7559768</v>
       </c>
       <c r="O5">
-        <v>34.354274084</v>
+        <v>34.257032112</v>
       </c>
       <c r="P5">
-        <v>66.68770851599999</v>
+        <v>66.49894468799999</v>
       </c>
       <c r="Q5">
-        <v>92.787708516</v>
+        <v>92.598944688</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09410415100639898</v>
+        <v>0.09443966427995829</v>
       </c>
       <c r="T5">
-        <v>0.6295650176894175</v>
+        <v>0.6339378803855327</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>118.7621603011781</v>
+        <v>89.07162022588354</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09198999770875994</v>
+        <v>0.09170302894131288</v>
       </c>
       <c r="C6">
-        <v>494.3831997876857</v>
+        <v>491.3455604336801</v>
       </c>
       <c r="D6">
-        <v>423.6271997876856</v>
+        <v>426.2755604336801</v>
       </c>
       <c r="E6">
-        <v>-285.656</v>
+        <v>-279.97</v>
       </c>
       <c r="F6">
-        <v>22.744</v>
+        <v>28.43</v>
       </c>
       <c r="G6">
         <v>93.5</v>
@@ -1773,28 +1773,28 @@
         <v>101.9</v>
       </c>
       <c r="M6">
-        <v>1.1440232</v>
+        <v>1.430029</v>
       </c>
       <c r="N6">
-        <v>100.7559768</v>
+        <v>100.469971</v>
       </c>
       <c r="O6">
-        <v>34.257032112</v>
+        <v>34.15979014</v>
       </c>
       <c r="P6">
-        <v>66.49894468799999</v>
+        <v>66.31018085999999</v>
       </c>
       <c r="Q6">
-        <v>92.598944688</v>
+        <v>92.41018086</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09443966427995829</v>
+        <v>0.09478224099085567</v>
       </c>
       <c r="T6">
-        <v>0.6339378803855327</v>
+        <v>0.6384028033489344</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>89.07162022588354</v>
+        <v>71.25729618070683</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09170302894131288</v>
+        <v>0.0914160601738658</v>
       </c>
       <c r="C7">
-        <v>491.3455604336801</v>
+        <v>488.3412425365232</v>
       </c>
       <c r="D7">
-        <v>426.2755604336801</v>
+        <v>428.9572425365232</v>
       </c>
       <c r="E7">
-        <v>-279.97</v>
+        <v>-274.284</v>
       </c>
       <c r="F7">
-        <v>28.43</v>
+        <v>34.116</v>
       </c>
       <c r="G7">
         <v>93.5</v>
@@ -1855,28 +1855,28 @@
         <v>101.9</v>
       </c>
       <c r="M7">
-        <v>1.430029</v>
+        <v>1.7160348</v>
       </c>
       <c r="N7">
-        <v>100.469971</v>
+        <v>100.1839652</v>
       </c>
       <c r="O7">
-        <v>34.15979014</v>
+        <v>34.062548168</v>
       </c>
       <c r="P7">
-        <v>66.31018085999999</v>
+        <v>66.12141703199998</v>
       </c>
       <c r="Q7">
-        <v>92.41018086</v>
+        <v>92.22141703199999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09478224099085567</v>
+        <v>0.09513210656794235</v>
       </c>
       <c r="T7">
-        <v>0.6384028033489344</v>
+        <v>0.6429627246732595</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>71.25729618070683</v>
+        <v>59.38108015058902</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0914160601738658</v>
+        <v>0.09112909140641874</v>
       </c>
       <c r="C8">
-        <v>488.3412425365232</v>
+        <v>485.3708789492301</v>
       </c>
       <c r="D8">
-        <v>428.9572425365232</v>
+        <v>431.6728789492302</v>
       </c>
       <c r="E8">
-        <v>-274.284</v>
+        <v>-268.598</v>
       </c>
       <c r="F8">
-        <v>34.11599999999999</v>
+        <v>39.80199999999999</v>
       </c>
       <c r="G8">
         <v>93.5</v>
@@ -1937,28 +1937,28 @@
         <v>101.9</v>
       </c>
       <c r="M8">
-        <v>1.7160348</v>
+        <v>2.0020406</v>
       </c>
       <c r="N8">
-        <v>100.1839652</v>
+        <v>99.89795939999999</v>
       </c>
       <c r="O8">
-        <v>34.062548168</v>
+        <v>33.965306196</v>
       </c>
       <c r="P8">
-        <v>66.12141703199998</v>
+        <v>65.93265320399999</v>
       </c>
       <c r="Q8">
-        <v>92.22141703199999</v>
+        <v>92.032653204</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09513210656794235</v>
+        <v>0.09548949613593413</v>
       </c>
       <c r="T8">
-        <v>0.6429627246732595</v>
+        <v>0.6476207088217637</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>59.38108015058903</v>
+        <v>50.89806870050488</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09112909140641873</v>
+        <v>0.09084212263897168</v>
       </c>
       <c r="C9">
-        <v>485.3708789492304</v>
+        <v>482.4351186527472</v>
       </c>
       <c r="D9">
-        <v>431.6728789492303</v>
+        <v>434.4231186527472</v>
       </c>
       <c r="E9">
-        <v>-268.598</v>
+        <v>-262.912</v>
       </c>
       <c r="F9">
-        <v>39.802</v>
+        <v>45.48799999999999</v>
       </c>
       <c r="G9">
         <v>93.5</v>
@@ -2019,28 +2019,28 @@
         <v>101.9</v>
       </c>
       <c r="M9">
-        <v>2.0020406</v>
+        <v>2.288046399999999</v>
       </c>
       <c r="N9">
-        <v>99.89795939999999</v>
+        <v>99.61195359999999</v>
       </c>
       <c r="O9">
-        <v>33.965306196</v>
+        <v>33.868064224</v>
       </c>
       <c r="P9">
-        <v>65.93265320399999</v>
+        <v>65.743889376</v>
       </c>
       <c r="Q9">
-        <v>92.032653204</v>
+        <v>91.84388937600001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09548949613593413</v>
+        <v>0.09585465504236053</v>
       </c>
       <c r="T9">
-        <v>0.6476207088217638</v>
+        <v>0.6523799534952355</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>50.89806870050487</v>
+        <v>44.53581011294177</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09084212263897168</v>
+        <v>0.09055515387152462</v>
       </c>
       <c r="C10">
-        <v>482.4351186527472</v>
+        <v>479.5346272730094</v>
       </c>
       <c r="D10">
-        <v>434.4231186527472</v>
+        <v>437.2086272730093</v>
       </c>
       <c r="E10">
-        <v>-262.912</v>
+        <v>-257.226</v>
       </c>
       <c r="F10">
-        <v>45.48799999999999</v>
+        <v>51.17399999999999</v>
       </c>
       <c r="G10">
         <v>93.5</v>
@@ -2101,28 +2101,28 @@
         <v>101.9</v>
       </c>
       <c r="M10">
-        <v>2.288046399999999</v>
+        <v>2.5740522</v>
       </c>
       <c r="N10">
-        <v>99.61195359999999</v>
+        <v>99.32594779999999</v>
       </c>
       <c r="O10">
-        <v>33.868064224</v>
+        <v>33.770822252</v>
       </c>
       <c r="P10">
-        <v>65.743889376</v>
+        <v>65.55512554799999</v>
       </c>
       <c r="Q10">
-        <v>91.84388937600001</v>
+        <v>91.655125548</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09585465504236053</v>
+        <v>0.09622783941925782</v>
       </c>
       <c r="T10">
-        <v>0.6523799534952355</v>
+        <v>0.6572437969527395</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>44.53581011294177</v>
+        <v>39.58738676705935</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09055515387152462</v>
+        <v>0.09026818510407755</v>
       </c>
       <c r="C11">
-        <v>479.5346272730094</v>
+        <v>476.6700876180201</v>
       </c>
       <c r="D11">
-        <v>437.2086272730093</v>
+        <v>440.0300876180202</v>
       </c>
       <c r="E11">
-        <v>-257.226</v>
+        <v>-251.54</v>
       </c>
       <c r="F11">
-        <v>51.17399999999999</v>
+        <v>56.85999999999999</v>
       </c>
       <c r="G11">
         <v>93.5</v>
@@ -2183,28 +2183,28 @@
         <v>101.9</v>
       </c>
       <c r="M11">
-        <v>2.5740522</v>
+        <v>2.860057999999999</v>
       </c>
       <c r="N11">
-        <v>99.32594779999999</v>
+        <v>99.039942</v>
       </c>
       <c r="O11">
-        <v>33.770822252</v>
+        <v>33.67358028</v>
       </c>
       <c r="P11">
-        <v>65.55512554799999</v>
+        <v>65.36636171999999</v>
       </c>
       <c r="Q11">
-        <v>91.655125548</v>
+        <v>91.46636171999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09622783941925782</v>
+        <v>0.09660931678230839</v>
       </c>
       <c r="T11">
-        <v>0.6572437969527395</v>
+        <v>0.6622157258204103</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>39.58738676705935</v>
+        <v>35.62864809035342</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09026818510407755</v>
+        <v>0.08998121633663049</v>
       </c>
       <c r="C12">
-        <v>476.6700876180201</v>
+        <v>473.842200235863</v>
       </c>
       <c r="D12">
-        <v>440.0300876180202</v>
+        <v>442.8882002358631</v>
       </c>
       <c r="E12">
-        <v>-251.54</v>
+        <v>-245.854</v>
       </c>
       <c r="F12">
-        <v>56.85999999999999</v>
+        <v>62.54599999999999</v>
       </c>
       <c r="G12">
         <v>93.5</v>
@@ -2265,28 +2265,28 @@
         <v>101.9</v>
       </c>
       <c r="M12">
-        <v>2.860058</v>
+        <v>3.146063799999999</v>
       </c>
       <c r="N12">
-        <v>99.039942</v>
+        <v>98.7539362</v>
       </c>
       <c r="O12">
-        <v>33.67358028</v>
+        <v>33.576338308</v>
       </c>
       <c r="P12">
-        <v>65.36636171999999</v>
+        <v>65.17759789199999</v>
       </c>
       <c r="Q12">
-        <v>91.46636171999999</v>
+        <v>91.277597892</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09660931678230839</v>
+        <v>0.09699936667037135</v>
       </c>
       <c r="T12">
-        <v>0.6622157258204103</v>
+        <v>0.6672993834266805</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>35.62864809035342</v>
+        <v>32.38968008213947</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08998121633663049</v>
+        <v>0.08969424756918344</v>
       </c>
       <c r="C13">
-        <v>473.842200235863</v>
+        <v>471.0516839945994</v>
       </c>
       <c r="D13">
-        <v>442.8882002358631</v>
+        <v>445.7836839945995</v>
       </c>
       <c r="E13">
-        <v>-245.854</v>
+        <v>-240.168</v>
       </c>
       <c r="F13">
-        <v>62.54599999999999</v>
+        <v>68.23199999999999</v>
       </c>
       <c r="G13">
         <v>93.5</v>
@@ -2347,28 +2347,28 @@
         <v>101.9</v>
       </c>
       <c r="M13">
-        <v>3.146063799999999</v>
+        <v>3.432069599999999</v>
       </c>
       <c r="N13">
-        <v>98.7539362</v>
+        <v>98.46793039999999</v>
       </c>
       <c r="O13">
-        <v>33.576338308</v>
+        <v>33.479096336</v>
       </c>
       <c r="P13">
-        <v>65.17759789199999</v>
+        <v>64.98883406399999</v>
       </c>
       <c r="Q13">
-        <v>91.277597892</v>
+        <v>91.088834064</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09699936667037135</v>
+        <v>0.09739828132861754</v>
       </c>
       <c r="T13">
-        <v>0.6672993834266805</v>
+        <v>0.6724985787058205</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.38968008213947</v>
+        <v>29.69054007529451</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08969424756918344</v>
+        <v>0.08940727880173636</v>
       </c>
       <c r="C14">
-        <v>471.0516839945994</v>
+        <v>468.2992766850668</v>
       </c>
       <c r="D14">
-        <v>445.7836839945995</v>
+        <v>448.7172766850668</v>
       </c>
       <c r="E14">
-        <v>-240.168</v>
+        <v>-234.482</v>
       </c>
       <c r="F14">
-        <v>68.23199999999999</v>
+        <v>73.91799999999999</v>
       </c>
       <c r="G14">
         <v>93.5</v>
@@ -2429,28 +2429,28 @@
         <v>101.9</v>
       </c>
       <c r="M14">
-        <v>3.432069599999999</v>
+        <v>3.7180754</v>
       </c>
       <c r="N14">
-        <v>98.46793039999999</v>
+        <v>98.18192459999999</v>
       </c>
       <c r="O14">
-        <v>33.479096336</v>
+        <v>33.381854364</v>
       </c>
       <c r="P14">
-        <v>64.98883406399999</v>
+        <v>64.80007023599998</v>
       </c>
       <c r="Q14">
-        <v>91.088834064</v>
+        <v>90.90007023599999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09739828132861754</v>
+        <v>0.09780636643877744</v>
       </c>
       <c r="T14">
-        <v>0.6724985787058205</v>
+        <v>0.6778172957155154</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.69054007529451</v>
+        <v>27.40665237719493</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08940727880173636</v>
+        <v>0.0891203100342893</v>
       </c>
       <c r="C15">
-        <v>468.2992766850668</v>
+        <v>465.5857356476318</v>
       </c>
       <c r="D15">
-        <v>448.7172766850668</v>
+        <v>451.6897356476318</v>
       </c>
       <c r="E15">
-        <v>-234.482</v>
+        <v>-228.796</v>
       </c>
       <c r="F15">
-        <v>73.91799999999999</v>
+        <v>79.604</v>
       </c>
       <c r="G15">
         <v>93.5</v>
@@ -2511,28 +2511,28 @@
         <v>101.9</v>
       </c>
       <c r="M15">
-        <v>3.7180754</v>
+        <v>4.0040812</v>
       </c>
       <c r="N15">
-        <v>98.18192459999999</v>
+        <v>97.89591879999999</v>
       </c>
       <c r="O15">
-        <v>33.381854364</v>
+        <v>33.284612392</v>
       </c>
       <c r="P15">
-        <v>64.80007023599998</v>
+        <v>64.61130640799999</v>
       </c>
       <c r="Q15">
-        <v>90.90007023599999</v>
+        <v>90.711306408</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09780636643877744</v>
+        <v>0.0982239419003364</v>
       </c>
       <c r="T15">
-        <v>0.6778172957155154</v>
+        <v>0.6832597038184589</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.40665237719493</v>
+        <v>25.44903435025244</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0891203100342893</v>
+        <v>0.08883334126684224</v>
       </c>
       <c r="C16">
-        <v>465.5857356476318</v>
+        <v>462.9118384240242</v>
       </c>
       <c r="D16">
-        <v>451.6897356476318</v>
+        <v>454.7018384240241</v>
       </c>
       <c r="E16">
-        <v>-228.796</v>
+        <v>-223.11</v>
       </c>
       <c r="F16">
-        <v>79.604</v>
+        <v>85.28999999999999</v>
       </c>
       <c r="G16">
         <v>93.5</v>
@@ -2593,28 +2593,28 @@
         <v>101.9</v>
       </c>
       <c r="M16">
-        <v>4.0040812</v>
+        <v>4.290087</v>
       </c>
       <c r="N16">
-        <v>97.89591879999999</v>
+        <v>97.60991299999999</v>
       </c>
       <c r="O16">
-        <v>33.284612392</v>
+        <v>33.18737042</v>
       </c>
       <c r="P16">
-        <v>64.61130640799999</v>
+        <v>64.42254258</v>
       </c>
       <c r="Q16">
-        <v>90.711306408</v>
+        <v>90.52254258000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0982239419003364</v>
+        <v>0.09865134266687323</v>
       </c>
       <c r="T16">
-        <v>0.6832597038184589</v>
+        <v>0.6888301685826482</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.44903435025244</v>
+        <v>23.75243206023561</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08883334126684224</v>
+        <v>0.08854637249939518</v>
       </c>
       <c r="C17">
-        <v>462.9118384240242</v>
+        <v>460.2783834354236</v>
       </c>
       <c r="D17">
-        <v>454.7018384240241</v>
+        <v>457.7543834354236</v>
       </c>
       <c r="E17">
-        <v>-223.11</v>
+        <v>-217.424</v>
       </c>
       <c r="F17">
-        <v>85.28999999999998</v>
+        <v>90.97599999999998</v>
       </c>
       <c r="G17">
         <v>93.5</v>
@@ -2675,28 +2675,28 @@
         <v>101.9</v>
       </c>
       <c r="M17">
-        <v>4.290086999999999</v>
+        <v>4.576092799999999</v>
       </c>
       <c r="N17">
-        <v>97.60991299999999</v>
+        <v>97.32390719999999</v>
       </c>
       <c r="O17">
-        <v>33.18737042</v>
+        <v>33.090128448</v>
       </c>
       <c r="P17">
-        <v>64.42254258</v>
+        <v>64.23377875199999</v>
       </c>
       <c r="Q17">
-        <v>90.52254258000001</v>
+        <v>90.333778752</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09865134266687323</v>
+        <v>0.09908891964213712</v>
       </c>
       <c r="T17">
-        <v>0.6888301685826482</v>
+        <v>0.6945332634602707</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.75243206023561</v>
+        <v>22.26790505647089</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08854637249939518</v>
+        <v>0.08825940373194809</v>
       </c>
       <c r="C18">
-        <v>460.2783834354236</v>
+        <v>457.686190688047</v>
       </c>
       <c r="D18">
-        <v>457.7543834354236</v>
+        <v>460.8481906880471</v>
       </c>
       <c r="E18">
-        <v>-217.424</v>
+        <v>-211.738</v>
       </c>
       <c r="F18">
-        <v>90.97599999999998</v>
+        <v>96.66199999999999</v>
       </c>
       <c r="G18">
         <v>93.5</v>
@@ -2757,28 +2757,28 @@
         <v>101.9</v>
       </c>
       <c r="M18">
-        <v>4.576092799999999</v>
+        <v>4.862098599999999</v>
       </c>
       <c r="N18">
-        <v>97.32390719999999</v>
+        <v>97.0379014</v>
       </c>
       <c r="O18">
-        <v>33.090128448</v>
+        <v>32.992886476</v>
       </c>
       <c r="P18">
-        <v>64.23377875199999</v>
+        <v>64.04501492399999</v>
       </c>
       <c r="Q18">
-        <v>90.333778752</v>
+        <v>90.14501492399999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09908891964213712</v>
+        <v>0.09953704064090133</v>
       </c>
       <c r="T18">
-        <v>0.6945332634602707</v>
+        <v>0.7003737823108478</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.26790505647089</v>
+        <v>20.95802828844318</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08825940373194809</v>
+        <v>0.08797243496450104</v>
       </c>
       <c r="C19">
-        <v>457.686190688047</v>
+        <v>455.1361025075393</v>
       </c>
       <c r="D19">
-        <v>460.8481906880471</v>
+        <v>463.9841025075394</v>
       </c>
       <c r="E19">
-        <v>-211.738</v>
+        <v>-206.052</v>
       </c>
       <c r="F19">
-        <v>96.66199999999999</v>
+        <v>102.348</v>
       </c>
       <c r="G19">
         <v>93.5</v>
@@ -2839,28 +2839,28 @@
         <v>101.9</v>
       </c>
       <c r="M19">
-        <v>4.862098599999999</v>
+        <v>5.148104399999999</v>
       </c>
       <c r="N19">
-        <v>97.0379014</v>
+        <v>96.7518956</v>
       </c>
       <c r="O19">
-        <v>32.992886476</v>
+        <v>32.895644504</v>
       </c>
       <c r="P19">
-        <v>64.04501492399999</v>
+        <v>63.85625109599999</v>
       </c>
       <c r="Q19">
-        <v>90.14501492399999</v>
+        <v>89.956251096</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09953704064090133</v>
+        <v>0.09999609142012322</v>
       </c>
       <c r="T19">
-        <v>0.7003737823108478</v>
+        <v>0.7063567528407073</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.95802828844318</v>
+        <v>19.79369338352967</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08797243496450105</v>
+        <v>0.08768546619705399</v>
       </c>
       <c r="C20">
-        <v>455.1361025075392</v>
+        <v>452.6289843035592</v>
       </c>
       <c r="D20">
-        <v>463.9841025075392</v>
+        <v>467.1629843035591</v>
       </c>
       <c r="E20">
-        <v>-206.052</v>
+        <v>-200.366</v>
       </c>
       <c r="F20">
-        <v>102.348</v>
+        <v>108.034</v>
       </c>
       <c r="G20">
         <v>93.5</v>
@@ -2921,28 +2921,28 @@
         <v>101.9</v>
       </c>
       <c r="M20">
-        <v>5.148104399999999</v>
+        <v>5.434110199999998</v>
       </c>
       <c r="N20">
-        <v>96.7518956</v>
+        <v>96.4658898</v>
       </c>
       <c r="O20">
-        <v>32.895644504</v>
+        <v>32.798402532</v>
       </c>
       <c r="P20">
-        <v>63.85625109599999</v>
+        <v>63.667487268</v>
       </c>
       <c r="Q20">
-        <v>89.956251096</v>
+        <v>89.767487268</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09999609142012322</v>
+        <v>0.1004664767864864</v>
       </c>
       <c r="T20">
-        <v>0.7063567528407073</v>
+        <v>0.7124874510379708</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.79369338352967</v>
+        <v>18.75192004755443</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08768546619705399</v>
+        <v>0.08739849742960691</v>
       </c>
       <c r="C21">
-        <v>452.6289843035592</v>
+        <v>450.165725366006</v>
       </c>
       <c r="D21">
-        <v>467.1629843035591</v>
+        <v>470.3857253660061</v>
       </c>
       <c r="E21">
-        <v>-200.366</v>
+        <v>-194.68</v>
       </c>
       <c r="F21">
-        <v>108.034</v>
+        <v>113.72</v>
       </c>
       <c r="G21">
         <v>93.5</v>
@@ -3003,28 +3003,28 @@
         <v>101.9</v>
       </c>
       <c r="M21">
-        <v>5.434110199999998</v>
+        <v>5.720115999999999</v>
       </c>
       <c r="N21">
-        <v>96.4658898</v>
+        <v>96.17988399999999</v>
       </c>
       <c r="O21">
-        <v>32.798402532</v>
+        <v>32.70116056</v>
       </c>
       <c r="P21">
-        <v>63.667487268</v>
+        <v>63.47872343999999</v>
       </c>
       <c r="Q21">
-        <v>89.767487268</v>
+        <v>89.57872344</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1004664767864864</v>
+        <v>0.1009486217870086</v>
       </c>
       <c r="T21">
-        <v>0.7124874510379708</v>
+        <v>0.7187714166901659</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.75192004755443</v>
+        <v>17.81432404517671</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08739849742960691</v>
+        <v>0.08711152866215986</v>
       </c>
       <c r="C22">
-        <v>450.165725366006</v>
+        <v>447.7472396944365</v>
       </c>
       <c r="D22">
-        <v>470.3857253660061</v>
+        <v>473.6532396944365</v>
       </c>
       <c r="E22">
-        <v>-194.68</v>
+        <v>-188.994</v>
       </c>
       <c r="F22">
-        <v>113.72</v>
+        <v>119.406</v>
       </c>
       <c r="G22">
         <v>93.5</v>
@@ -3085,28 +3085,28 @@
         <v>101.9</v>
       </c>
       <c r="M22">
-        <v>5.720115999999999</v>
+        <v>6.006121799999999</v>
       </c>
       <c r="N22">
-        <v>96.17988399999999</v>
+        <v>95.89387819999999</v>
       </c>
       <c r="O22">
-        <v>32.70116056</v>
+        <v>32.603918588</v>
       </c>
       <c r="P22">
-        <v>63.47872343999999</v>
+        <v>63.28995961199999</v>
       </c>
       <c r="Q22">
-        <v>89.57872344</v>
+        <v>89.389959612</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1009486217870086</v>
+        <v>0.1014429729900758</v>
       </c>
       <c r="T22">
-        <v>0.7187714166901659</v>
+        <v>0.7252144700803913</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.81432404517671</v>
+        <v>16.96602290016829</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08711152866215985</v>
+        <v>0.08682455989471279</v>
       </c>
       <c r="C23">
-        <v>447.7472396944368</v>
+        <v>445.3744668622908</v>
       </c>
       <c r="D23">
-        <v>473.6532396944366</v>
+        <v>476.9664668622908</v>
       </c>
       <c r="E23">
-        <v>-188.994</v>
+        <v>-183.308</v>
       </c>
       <c r="F23">
-        <v>119.406</v>
+        <v>125.092</v>
       </c>
       <c r="G23">
         <v>93.5</v>
@@ -3167,28 +3167,28 @@
         <v>101.9</v>
       </c>
       <c r="M23">
-        <v>6.006121799999999</v>
+        <v>6.292127599999999</v>
       </c>
       <c r="N23">
-        <v>95.89387819999999</v>
+        <v>95.60787239999999</v>
       </c>
       <c r="O23">
-        <v>32.603918588</v>
+        <v>32.506676616</v>
       </c>
       <c r="P23">
-        <v>63.28995961199999</v>
+        <v>63.10119578399999</v>
       </c>
       <c r="Q23">
-        <v>89.389959612</v>
+        <v>89.20119578399999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1014429729900758</v>
+        <v>0.1019499998650164</v>
       </c>
       <c r="T23">
-        <v>0.7252144700803911</v>
+        <v>0.7318227299678017</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.96602290016829</v>
+        <v>16.19484004106973</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08682455989471279</v>
+        <v>0.08653759112726572</v>
       </c>
       <c r="C24">
-        <v>445.3744668622908</v>
+        <v>443.0483729176451</v>
       </c>
       <c r="D24">
-        <v>476.9664668622908</v>
+        <v>480.3263729176451</v>
       </c>
       <c r="E24">
-        <v>-183.308</v>
+        <v>-177.622</v>
       </c>
       <c r="F24">
-        <v>125.092</v>
+        <v>130.778</v>
       </c>
       <c r="G24">
         <v>93.5</v>
@@ -3249,28 +3249,28 @@
         <v>101.9</v>
       </c>
       <c r="M24">
-        <v>6.292127599999999</v>
+        <v>6.5781334</v>
       </c>
       <c r="N24">
-        <v>95.60787239999999</v>
+        <v>95.32186659999999</v>
       </c>
       <c r="O24">
-        <v>32.506676616</v>
+        <v>32.409434644</v>
       </c>
       <c r="P24">
-        <v>63.10119578399999</v>
+        <v>62.91243195599999</v>
       </c>
       <c r="Q24">
-        <v>89.20119578399999</v>
+        <v>89.012431956</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1019499998650164</v>
+        <v>0.1024701962691763</v>
       </c>
       <c r="T24">
-        <v>0.7318227299678017</v>
+        <v>0.7386026329691711</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.19484004106973</v>
+        <v>15.49071656102322</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08653759112726572</v>
+        <v>0.08625062235981867</v>
       </c>
       <c r="C25">
-        <v>443.0483729176451</v>
+        <v>440.7699513223078</v>
       </c>
       <c r="D25">
-        <v>480.3263729176451</v>
+        <v>483.7339513223079</v>
       </c>
       <c r="E25">
-        <v>-177.622</v>
+        <v>-171.936</v>
       </c>
       <c r="F25">
-        <v>130.778</v>
+        <v>136.464</v>
       </c>
       <c r="G25">
         <v>93.5</v>
@@ -3331,28 +3331,28 @@
         <v>101.9</v>
       </c>
       <c r="M25">
-        <v>6.5781334</v>
+        <v>6.864139199999999</v>
       </c>
       <c r="N25">
-        <v>95.32186659999999</v>
+        <v>95.03586079999999</v>
       </c>
       <c r="O25">
-        <v>32.409434644</v>
+        <v>32.312192672</v>
       </c>
       <c r="P25">
-        <v>62.91243195599999</v>
+        <v>62.72366812799999</v>
       </c>
       <c r="Q25">
-        <v>89.012431956</v>
+        <v>88.82366812800001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1024701962691763</v>
+        <v>0.103004082052393</v>
       </c>
       <c r="T25">
-        <v>0.7386026329691711</v>
+        <v>0.7455609544705765</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.49071656102322</v>
+        <v>14.84527003764726</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08625062235981866</v>
+        <v>0.0859636535923716</v>
       </c>
       <c r="C26">
-        <v>440.7699513223081</v>
+        <v>438.5402239311733</v>
       </c>
       <c r="D26">
-        <v>483.7339513223081</v>
+        <v>487.1902239311733</v>
       </c>
       <c r="E26">
-        <v>-171.936</v>
+        <v>-166.25</v>
       </c>
       <c r="F26">
-        <v>136.464</v>
+        <v>142.15</v>
       </c>
       <c r="G26">
         <v>93.5</v>
@@ -3413,28 +3413,28 @@
         <v>101.9</v>
       </c>
       <c r="M26">
-        <v>6.864139199999999</v>
+        <v>7.150144999999998</v>
       </c>
       <c r="N26">
-        <v>95.03586079999999</v>
+        <v>94.749855</v>
       </c>
       <c r="O26">
-        <v>32.312192672</v>
+        <v>32.2149507</v>
       </c>
       <c r="P26">
-        <v>62.72366812799999</v>
+        <v>62.53490429999999</v>
       </c>
       <c r="Q26">
-        <v>88.82366812800001</v>
+        <v>88.6349043</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.103004082052393</v>
+        <v>0.1035522047898288</v>
       </c>
       <c r="T26">
-        <v>0.7455609544705764</v>
+        <v>0.7527048312120193</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.84527003764726</v>
+        <v>14.25145923614137</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0859636535923716</v>
+        <v>0.08567668482492452</v>
       </c>
       <c r="C27">
-        <v>438.5402239311733</v>
+        <v>436.3602420138601</v>
       </c>
       <c r="D27">
-        <v>487.1902239311733</v>
+        <v>490.6962420138601</v>
       </c>
       <c r="E27">
-        <v>-166.25</v>
+        <v>-160.564</v>
       </c>
       <c r="F27">
-        <v>142.15</v>
+        <v>147.836</v>
       </c>
       <c r="G27">
         <v>93.5</v>
@@ -3495,28 +3495,28 @@
         <v>101.9</v>
       </c>
       <c r="M27">
-        <v>7.150144999999998</v>
+        <v>7.436150799999999</v>
       </c>
       <c r="N27">
-        <v>94.749855</v>
+        <v>94.4638492</v>
       </c>
       <c r="O27">
-        <v>32.2149507</v>
+        <v>32.117708728</v>
       </c>
       <c r="P27">
-        <v>62.53490429999999</v>
+        <v>62.34614047199999</v>
       </c>
       <c r="Q27">
-        <v>88.6349043</v>
+        <v>88.446140472</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1035522047898288</v>
+        <v>0.1041151416553034</v>
       </c>
       <c r="T27">
-        <v>0.7527048312120193</v>
+        <v>0.7600417857032308</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.25145923614137</v>
+        <v>13.70332618859747</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08567668482492452</v>
+        <v>0.08538971605747746</v>
       </c>
       <c r="C28">
-        <v>436.3602420138601</v>
+        <v>434.2310873207875</v>
       </c>
       <c r="D28">
-        <v>490.6962420138601</v>
+        <v>494.2530873207875</v>
       </c>
       <c r="E28">
-        <v>-160.564</v>
+        <v>-154.878</v>
       </c>
       <c r="F28">
-        <v>147.836</v>
+        <v>153.522</v>
       </c>
       <c r="G28">
         <v>93.5</v>
@@ -3577,28 +3577,28 @@
         <v>101.9</v>
       </c>
       <c r="M28">
-        <v>7.436150799999999</v>
+        <v>7.722156599999999</v>
       </c>
       <c r="N28">
-        <v>94.4638492</v>
+        <v>94.17784339999999</v>
       </c>
       <c r="O28">
-        <v>32.117708728</v>
+        <v>32.020466756</v>
       </c>
       <c r="P28">
-        <v>62.34614047199999</v>
+        <v>62.15737664399999</v>
       </c>
       <c r="Q28">
-        <v>88.446140472</v>
+        <v>88.257376644</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1041151416553034</v>
+        <v>0.1046935014485993</v>
       </c>
       <c r="T28">
-        <v>0.7600417857032308</v>
+        <v>0.7675797526462562</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.70332618859747</v>
+        <v>13.19579558901978</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08538971605747746</v>
+        <v>0.0853799472900304</v>
       </c>
       <c r="C29">
-        <v>434.2310873207875</v>
+        <v>428.6670744329643</v>
       </c>
       <c r="D29">
-        <v>494.2530873207875</v>
+        <v>494.3750744329644</v>
       </c>
       <c r="E29">
-        <v>-154.878</v>
+        <v>-149.192</v>
       </c>
       <c r="F29">
-        <v>153.522</v>
+        <v>159.208</v>
       </c>
       <c r="G29">
         <v>93.5</v>
@@ -3659,45 +3659,45 @@
         <v>101.9</v>
       </c>
       <c r="M29">
-        <v>7.722156599999999</v>
+        <v>8.246974399999999</v>
       </c>
       <c r="N29">
-        <v>94.17784339999999</v>
+        <v>93.65302559999999</v>
       </c>
       <c r="O29">
-        <v>32.020466756</v>
+        <v>31.842028704</v>
       </c>
       <c r="P29">
-        <v>62.15737664399999</v>
+        <v>61.81099689599999</v>
       </c>
       <c r="Q29">
-        <v>88.257376644</v>
+        <v>87.910996896</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1046935014485993</v>
+        <v>0.1052879267917089</v>
       </c>
       <c r="T29">
-        <v>0.7675797526462562</v>
+        <v>0.7753271075599214</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.34</v>
       </c>
       <c r="W29">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>13.19579558901978</v>
+        <v>12.35604660055693</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0853799472900304</v>
+        <v>0.08510287852258333</v>
       </c>
       <c r="C30">
-        <v>428.6670744329643</v>
+        <v>426.4662108320958</v>
       </c>
       <c r="D30">
-        <v>494.3750744329644</v>
+        <v>497.8602108320958</v>
       </c>
       <c r="E30">
-        <v>-149.192</v>
+        <v>-143.506</v>
       </c>
       <c r="F30">
-        <v>159.208</v>
+        <v>164.894</v>
       </c>
       <c r="G30">
         <v>93.5</v>
@@ -3741,28 +3741,28 @@
         <v>101.9</v>
       </c>
       <c r="M30">
-        <v>8.246974399999999</v>
+        <v>8.5415092</v>
       </c>
       <c r="N30">
-        <v>93.65302559999999</v>
+        <v>93.3584908</v>
       </c>
       <c r="O30">
-        <v>31.842028704</v>
+        <v>31.741886872</v>
       </c>
       <c r="P30">
-        <v>61.81099689599999</v>
+        <v>61.616603928</v>
       </c>
       <c r="Q30">
-        <v>87.910996896</v>
+        <v>87.71660392800001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1052879267917089</v>
+        <v>0.1058990965106808</v>
       </c>
       <c r="T30">
-        <v>0.7753271075599214</v>
+        <v>0.7832926978232673</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.35604660055693</v>
+        <v>11.92997602812393</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08510287852258333</v>
+        <v>0.08482580975513627</v>
       </c>
       <c r="C31">
-        <v>426.4662108320959</v>
+        <v>424.3148335815451</v>
       </c>
       <c r="D31">
-        <v>497.8602108320958</v>
+        <v>501.394833581545</v>
       </c>
       <c r="E31">
-        <v>-143.506</v>
+        <v>-137.82</v>
       </c>
       <c r="F31">
-        <v>164.8939999999999</v>
+        <v>170.58</v>
       </c>
       <c r="G31">
         <v>93.5</v>
@@ -3823,28 +3823,28 @@
         <v>101.9</v>
       </c>
       <c r="M31">
-        <v>8.541509199999997</v>
+        <v>8.836043999999998</v>
       </c>
       <c r="N31">
-        <v>93.3584908</v>
+        <v>93.06395599999999</v>
       </c>
       <c r="O31">
-        <v>31.741886872</v>
+        <v>31.64174504</v>
       </c>
       <c r="P31">
-        <v>61.616603928</v>
+        <v>61.42221095999999</v>
       </c>
       <c r="Q31">
-        <v>87.71660392800001</v>
+        <v>87.52221096</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1058990965106808</v>
+        <v>0.1065277282216233</v>
       </c>
       <c r="T31">
-        <v>0.7832926978232673</v>
+        <v>0.7914858763798517</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.92997602812393</v>
+        <v>11.5323101605198</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08482580975513627</v>
+        <v>0.08454874098768921</v>
       </c>
       <c r="C32">
-        <v>424.3148335815451</v>
+        <v>422.2140042220286</v>
       </c>
       <c r="D32">
-        <v>501.394833581545</v>
+        <v>504.9800042220286</v>
       </c>
       <c r="E32">
-        <v>-137.82</v>
+        <v>-132.134</v>
       </c>
       <c r="F32">
-        <v>170.58</v>
+        <v>176.266</v>
       </c>
       <c r="G32">
         <v>93.5</v>
@@ -3905,28 +3905,28 @@
         <v>101.9</v>
       </c>
       <c r="M32">
-        <v>8.836043999999998</v>
+        <v>9.130578799999999</v>
       </c>
       <c r="N32">
-        <v>93.06395599999999</v>
+        <v>92.7694212</v>
       </c>
       <c r="O32">
-        <v>31.64174504</v>
+        <v>31.541603208</v>
       </c>
       <c r="P32">
-        <v>61.42221095999999</v>
+        <v>61.227817992</v>
       </c>
       <c r="Q32">
-        <v>87.52221096</v>
+        <v>87.32781799200001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1065277282216233</v>
+        <v>0.1071745811415786</v>
       </c>
       <c r="T32">
-        <v>0.7914858763798517</v>
+        <v>0.7999165383728587</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.5323101605198</v>
+        <v>11.16030015534174</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08454874098768921</v>
+        <v>0.08427167222024215</v>
       </c>
       <c r="C33">
-        <v>422.2140042220286</v>
+        <v>420.1648148746622</v>
       </c>
       <c r="D33">
-        <v>504.9800042220286</v>
+        <v>508.6168148746622</v>
       </c>
       <c r="E33">
-        <v>-132.134</v>
+        <v>-126.448</v>
       </c>
       <c r="F33">
-        <v>176.266</v>
+        <v>181.952</v>
       </c>
       <c r="G33">
         <v>93.5</v>
@@ -3987,28 +3987,28 @@
         <v>101.9</v>
       </c>
       <c r="M33">
-        <v>9.130578799999999</v>
+        <v>9.425113599999998</v>
       </c>
       <c r="N33">
-        <v>92.7694212</v>
+        <v>92.47488639999999</v>
       </c>
       <c r="O33">
-        <v>31.541603208</v>
+        <v>31.441461376</v>
       </c>
       <c r="P33">
-        <v>61.227817992</v>
+        <v>61.03342502399999</v>
       </c>
       <c r="Q33">
-        <v>87.32781799200001</v>
+        <v>87.13342502399999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1071745811415786</v>
+        <v>0.1078404591474149</v>
       </c>
       <c r="T33">
-        <v>0.7999165383728587</v>
+        <v>0.8085951610127188</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.16030015534174</v>
+        <v>10.81154077548731</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08427167222024215</v>
+        <v>0.08399460345279508</v>
       </c>
       <c r="C34">
-        <v>420.1648148746622</v>
+        <v>418.1683893501334</v>
       </c>
       <c r="D34">
-        <v>508.6168148746622</v>
+        <v>512.3063893501334</v>
       </c>
       <c r="E34">
-        <v>-126.448</v>
+        <v>-120.762</v>
       </c>
       <c r="F34">
-        <v>181.952</v>
+        <v>187.638</v>
       </c>
       <c r="G34">
         <v>93.5</v>
@@ -4069,28 +4069,28 @@
         <v>101.9</v>
       </c>
       <c r="M34">
-        <v>9.425113599999998</v>
+        <v>9.719648399999999</v>
       </c>
       <c r="N34">
-        <v>92.47488639999999</v>
+        <v>92.18035159999999</v>
       </c>
       <c r="O34">
-        <v>31.441461376</v>
+        <v>31.341319544</v>
       </c>
       <c r="P34">
-        <v>61.03342502399999</v>
+        <v>60.83903205599999</v>
       </c>
       <c r="Q34">
-        <v>87.13342502399999</v>
+        <v>86.939032056</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1078404591474149</v>
+        <v>0.1085262141086494</v>
       </c>
       <c r="T34">
-        <v>0.8085951610127188</v>
+        <v>0.8175328470149629</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.81154077548731</v>
+        <v>10.48391832774527</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08399460345279508</v>
+        <v>0.083717534685348</v>
       </c>
       <c r="C35">
-        <v>418.1683893501334</v>
+        <v>416.2258843065015</v>
       </c>
       <c r="D35">
-        <v>512.3063893501334</v>
+        <v>516.0498843065014</v>
       </c>
       <c r="E35">
-        <v>-120.762</v>
+        <v>-115.076</v>
       </c>
       <c r="F35">
-        <v>187.638</v>
+        <v>193.324</v>
       </c>
       <c r="G35">
         <v>93.5</v>
@@ -4151,28 +4151,28 @@
         <v>101.9</v>
       </c>
       <c r="M35">
-        <v>9.719648399999999</v>
+        <v>10.0141832</v>
       </c>
       <c r="N35">
-        <v>92.18035159999999</v>
+        <v>91.88581679999999</v>
       </c>
       <c r="O35">
-        <v>31.341319544</v>
+        <v>31.241177712</v>
       </c>
       <c r="P35">
-        <v>60.83903205599999</v>
+        <v>60.64463908799999</v>
       </c>
       <c r="Q35">
-        <v>86.939032056</v>
+        <v>86.744639088</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1085262141086494</v>
+        <v>0.1092327495232546</v>
       </c>
       <c r="T35">
-        <v>0.8175328470149629</v>
+        <v>0.826741371986972</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.48391832774527</v>
+        <v>10.17556778869394</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.083717534685348</v>
+        <v>0.08344046591790096</v>
       </c>
       <c r="C36">
-        <v>416.2258843065015</v>
+        <v>414.3384904581322</v>
       </c>
       <c r="D36">
-        <v>516.0498843065014</v>
+        <v>519.8484904581322</v>
       </c>
       <c r="E36">
-        <v>-115.076</v>
+        <v>-109.39</v>
       </c>
       <c r="F36">
-        <v>193.324</v>
+        <v>199.01</v>
       </c>
       <c r="G36">
         <v>93.5</v>
@@ -4233,28 +4233,28 @@
         <v>101.9</v>
       </c>
       <c r="M36">
-        <v>10.0141832</v>
+        <v>10.308718</v>
       </c>
       <c r="N36">
-        <v>91.88581679999999</v>
+        <v>91.59128199999999</v>
       </c>
       <c r="O36">
-        <v>31.241177712</v>
+        <v>31.14103588</v>
       </c>
       <c r="P36">
-        <v>60.64463908799999</v>
+        <v>60.45024611999999</v>
       </c>
       <c r="Q36">
-        <v>86.744639088</v>
+        <v>86.55024612</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1092327495232546</v>
+        <v>0.1099610244890784</v>
       </c>
       <c r="T36">
-        <v>0.826741371986972</v>
+        <v>0.836233236188889</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.17556778869394</v>
+        <v>9.884837280445542</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08344046591790096</v>
+        <v>0.08356731715045389</v>
       </c>
       <c r="C37">
-        <v>414.3384904581322</v>
+        <v>406.9064458160758</v>
       </c>
       <c r="D37">
-        <v>519.8484904581322</v>
+        <v>518.1024458160758</v>
       </c>
       <c r="E37">
-        <v>-109.39</v>
+        <v>-103.704</v>
       </c>
       <c r="F37">
-        <v>199.01</v>
+        <v>204.696</v>
       </c>
       <c r="G37">
         <v>93.5</v>
@@ -4315,45 +4315,45 @@
         <v>101.9</v>
       </c>
       <c r="M37">
-        <v>10.308718</v>
+        <v>10.951236</v>
       </c>
       <c r="N37">
-        <v>91.59128199999999</v>
+        <v>90.948764</v>
       </c>
       <c r="O37">
-        <v>31.14103588</v>
+        <v>30.92257976</v>
       </c>
       <c r="P37">
-        <v>60.45024611999999</v>
+        <v>60.02618423999999</v>
       </c>
       <c r="Q37">
-        <v>86.55024612</v>
+        <v>86.12618424</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1099610244890784</v>
+        <v>0.1107120580475842</v>
       </c>
       <c r="T37">
-        <v>0.836233236188889</v>
+        <v>0.8460217211471159</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.34</v>
       </c>
       <c r="W37">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>9.884837280445542</v>
+        <v>9.304885768145258</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0835673171504539</v>
+        <v>0.08330146838300682</v>
       </c>
       <c r="C38">
-        <v>406.9064458160757</v>
+        <v>404.8932859092901</v>
       </c>
       <c r="D38">
-        <v>518.1024458160757</v>
+        <v>521.77528590929</v>
       </c>
       <c r="E38">
-        <v>-103.704</v>
+        <v>-98.018</v>
       </c>
       <c r="F38">
-        <v>204.696</v>
+        <v>210.382</v>
       </c>
       <c r="G38">
         <v>93.5</v>
@@ -4397,28 +4397,28 @@
         <v>101.9</v>
       </c>
       <c r="M38">
-        <v>10.951236</v>
+        <v>11.255437</v>
       </c>
       <c r="N38">
-        <v>90.948764</v>
+        <v>90.64456299999999</v>
       </c>
       <c r="O38">
-        <v>30.92257976</v>
+        <v>30.81915142</v>
       </c>
       <c r="P38">
-        <v>60.02618423999999</v>
+        <v>59.82541157999999</v>
       </c>
       <c r="Q38">
-        <v>86.12618424</v>
+        <v>85.92541158</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1107120580475842</v>
+        <v>0.1114869339412807</v>
       </c>
       <c r="T38">
-        <v>0.8460217211471158</v>
+        <v>0.8561209516595721</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.304885768145258</v>
+        <v>9.053402369006196</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08330146838300682</v>
+        <v>0.08303561961555976</v>
       </c>
       <c r="C39">
-        <v>404.8932859092901</v>
+        <v>402.932571484647</v>
       </c>
       <c r="D39">
-        <v>521.77528590929</v>
+        <v>525.500571484647</v>
       </c>
       <c r="E39">
-        <v>-98.018</v>
+        <v>-92.33200000000002</v>
       </c>
       <c r="F39">
-        <v>210.382</v>
+        <v>216.068</v>
       </c>
       <c r="G39">
         <v>93.5</v>
@@ -4479,28 +4479,28 @@
         <v>101.9</v>
       </c>
       <c r="M39">
-        <v>11.255437</v>
+        <v>11.559638</v>
       </c>
       <c r="N39">
-        <v>90.64456299999999</v>
+        <v>90.340362</v>
       </c>
       <c r="O39">
-        <v>30.81915142</v>
+        <v>30.71572308</v>
       </c>
       <c r="P39">
-        <v>59.82541157999999</v>
+        <v>59.62463892</v>
       </c>
       <c r="Q39">
-        <v>85.92541158</v>
+        <v>85.72463892</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1114869339412807</v>
+        <v>0.112286805831548</v>
       </c>
       <c r="T39">
-        <v>0.8561209516595721</v>
+        <v>0.8665459638014626</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.053402369006196</v>
+        <v>8.815154938242877</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08303561961555976</v>
+        <v>0.08276977084811271</v>
       </c>
       <c r="C40">
-        <v>402.932571484647</v>
+        <v>401.0254339448954</v>
       </c>
       <c r="D40">
-        <v>525.500571484647</v>
+        <v>529.2794339448953</v>
       </c>
       <c r="E40">
-        <v>-92.33200000000002</v>
+        <v>-86.64600000000002</v>
       </c>
       <c r="F40">
-        <v>216.068</v>
+        <v>221.754</v>
       </c>
       <c r="G40">
         <v>93.5</v>
@@ -4561,28 +4561,28 @@
         <v>101.9</v>
       </c>
       <c r="M40">
-        <v>11.559638</v>
+        <v>11.863839</v>
       </c>
       <c r="N40">
-        <v>90.340362</v>
+        <v>90.03616099999999</v>
       </c>
       <c r="O40">
-        <v>30.71572308</v>
+        <v>30.61229474</v>
       </c>
       <c r="P40">
-        <v>59.62463892</v>
+        <v>59.42386626</v>
       </c>
       <c r="Q40">
-        <v>85.72463892</v>
+        <v>85.52386626000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.112286805831548</v>
+        <v>0.113112903029693</v>
       </c>
       <c r="T40">
-        <v>0.8665459638014626</v>
+        <v>0.8773127796201363</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.815154938242877</v>
+        <v>8.589125324441778</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08276977084811271</v>
+        <v>0.08250392208066563</v>
       </c>
       <c r="C41">
-        <v>401.0254339448954</v>
+        <v>399.1730374720632</v>
       </c>
       <c r="D41">
-        <v>529.2794339448953</v>
+        <v>533.1130374720632</v>
       </c>
       <c r="E41">
-        <v>-86.64600000000002</v>
+        <v>-80.96000000000001</v>
       </c>
       <c r="F41">
-        <v>221.754</v>
+        <v>227.44</v>
       </c>
       <c r="G41">
         <v>93.5</v>
@@ -4643,28 +4643,28 @@
         <v>101.9</v>
       </c>
       <c r="M41">
-        <v>11.863839</v>
+        <v>12.16804</v>
       </c>
       <c r="N41">
-        <v>90.03616099999999</v>
+        <v>89.73195999999999</v>
       </c>
       <c r="O41">
-        <v>30.61229474</v>
+        <v>30.5088664</v>
       </c>
       <c r="P41">
-        <v>59.42386626</v>
+        <v>59.22309359999998</v>
       </c>
       <c r="Q41">
-        <v>85.52386626000001</v>
+        <v>85.32309359999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.113112903029693</v>
+        <v>0.1139665368011094</v>
       </c>
       <c r="T41">
-        <v>0.8773127796201363</v>
+        <v>0.8884384892994325</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.589125324441778</v>
+        <v>8.374397191330733</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08250392208066563</v>
+        <v>0.08223807331321857</v>
       </c>
       <c r="C42">
-        <v>399.1730374720632</v>
+        <v>397.3765802232299</v>
       </c>
       <c r="D42">
-        <v>533.1130374720632</v>
+        <v>537.0025802232299</v>
       </c>
       <c r="E42">
-        <v>-80.96000000000001</v>
+        <v>-75.274</v>
       </c>
       <c r="F42">
-        <v>227.44</v>
+        <v>233.126</v>
       </c>
       <c r="G42">
         <v>93.5</v>
@@ -4725,28 +4725,28 @@
         <v>101.9</v>
       </c>
       <c r="M42">
-        <v>12.16804</v>
+        <v>12.472241</v>
       </c>
       <c r="N42">
-        <v>89.73195999999999</v>
+        <v>89.42775899999999</v>
       </c>
       <c r="O42">
-        <v>30.5088664</v>
+        <v>30.40543806</v>
       </c>
       <c r="P42">
-        <v>59.22309359999998</v>
+        <v>59.02232093999999</v>
       </c>
       <c r="Q42">
-        <v>85.32309359999999</v>
+        <v>85.12232094000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1139665368011094</v>
+        <v>0.11484910731054</v>
       </c>
       <c r="T42">
-        <v>0.8884384892994325</v>
+        <v>0.8999413416797217</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.374397191330733</v>
+        <v>8.170143601298275</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08223807331321857</v>
+        <v>0.08197222454577151</v>
       </c>
       <c r="C43">
-        <v>397.3765802232299</v>
+        <v>395.6372955790297</v>
       </c>
       <c r="D43">
-        <v>537.0025802232299</v>
+        <v>540.9492955790297</v>
       </c>
       <c r="E43">
-        <v>-75.274</v>
+        <v>-69.58799999999999</v>
       </c>
       <c r="F43">
-        <v>233.126</v>
+        <v>238.812</v>
       </c>
       <c r="G43">
         <v>93.5</v>
@@ -4807,28 +4807,28 @@
         <v>101.9</v>
       </c>
       <c r="M43">
-        <v>12.472241</v>
+        <v>12.776442</v>
       </c>
       <c r="N43">
-        <v>89.42775899999999</v>
+        <v>89.12355799999999</v>
       </c>
       <c r="O43">
-        <v>30.40543806</v>
+        <v>30.30200972</v>
       </c>
       <c r="P43">
-        <v>59.02232093999999</v>
+        <v>58.82154827999999</v>
       </c>
       <c r="Q43">
-        <v>85.12232094000001</v>
+        <v>84.92154828</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.11484910731054</v>
+        <v>0.115762111285813</v>
       </c>
       <c r="T43">
-        <v>0.8999413416797217</v>
+        <v>0.9118408441420901</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.170143601298275</v>
+        <v>7.975616372695935</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08197222454577152</v>
+        <v>0.08170637577832444</v>
       </c>
       <c r="C44">
-        <v>395.6372955790295</v>
+        <v>393.9564534476181</v>
       </c>
       <c r="D44">
-        <v>540.9492955790295</v>
+        <v>544.954453447618</v>
       </c>
       <c r="E44">
-        <v>-69.58800000000002</v>
+        <v>-63.90200000000002</v>
       </c>
       <c r="F44">
-        <v>238.812</v>
+        <v>244.498</v>
       </c>
       <c r="G44">
         <v>93.5</v>
@@ -4889,28 +4889,28 @@
         <v>101.9</v>
       </c>
       <c r="M44">
-        <v>12.776442</v>
+        <v>13.080643</v>
       </c>
       <c r="N44">
-        <v>89.12355799999999</v>
+        <v>88.819357</v>
       </c>
       <c r="O44">
-        <v>30.30200972</v>
+        <v>30.19858138</v>
       </c>
       <c r="P44">
-        <v>58.82154827999999</v>
+        <v>58.62077562</v>
       </c>
       <c r="Q44">
-        <v>84.92154828</v>
+        <v>84.72077562000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.115762111285813</v>
+        <v>0.1167071504882885</v>
       </c>
       <c r="T44">
-        <v>0.91184084414209</v>
+        <v>0.9241578730066465</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.975616372695936</v>
+        <v>7.790136922168124</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08170637577832444</v>
+        <v>0.08144052701087737</v>
       </c>
       <c r="C45">
-        <v>393.9564534476181</v>
+        <v>392.3353616269957</v>
       </c>
       <c r="D45">
-        <v>544.954453447618</v>
+        <v>549.0193616269956</v>
       </c>
       <c r="E45">
-        <v>-63.90200000000002</v>
+        <v>-58.21600000000001</v>
       </c>
       <c r="F45">
-        <v>244.498</v>
+        <v>250.184</v>
       </c>
       <c r="G45">
         <v>93.5</v>
@@ -4971,28 +4971,28 @@
         <v>101.9</v>
       </c>
       <c r="M45">
-        <v>13.080643</v>
+        <v>13.384844</v>
       </c>
       <c r="N45">
-        <v>88.819357</v>
+        <v>88.51515599999999</v>
       </c>
       <c r="O45">
-        <v>30.19858138</v>
+        <v>30.09515304</v>
       </c>
       <c r="P45">
-        <v>58.62077562</v>
+        <v>58.42000295999999</v>
       </c>
       <c r="Q45">
-        <v>84.72077562000001</v>
+        <v>84.52000296</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1167071504882885</v>
+        <v>0.1176859410908525</v>
       </c>
       <c r="T45">
-        <v>0.9241578730066465</v>
+        <v>0.9369147957592229</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.790136922168124</v>
+        <v>7.613088355755211</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08144052701087737</v>
+        <v>0.08141227824343034</v>
       </c>
       <c r="C46">
-        <v>392.3353616269957</v>
+        <v>387.0848608715119</v>
       </c>
       <c r="D46">
-        <v>549.0193616269956</v>
+        <v>549.4548608715119</v>
       </c>
       <c r="E46">
-        <v>-58.21600000000001</v>
+        <v>-52.53</v>
       </c>
       <c r="F46">
-        <v>250.184</v>
+        <v>255.87</v>
       </c>
       <c r="G46">
         <v>93.5</v>
@@ -5053,45 +5053,45 @@
         <v>101.9</v>
       </c>
       <c r="M46">
-        <v>13.384844</v>
+        <v>13.893741</v>
       </c>
       <c r="N46">
-        <v>88.51515599999999</v>
+        <v>88.006259</v>
       </c>
       <c r="O46">
-        <v>30.09515304</v>
+        <v>29.92212806</v>
       </c>
       <c r="P46">
-        <v>58.42000295999999</v>
+        <v>58.08413093999999</v>
       </c>
       <c r="Q46">
-        <v>84.52000296</v>
+        <v>84.18413094</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1176859410908525</v>
+        <v>0.1187003240789642</v>
       </c>
       <c r="T46">
-        <v>0.9369147957592229</v>
+        <v>0.9501356066118931</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.34</v>
       </c>
       <c r="W46">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.613088355755211</v>
+        <v>7.334237769366797</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08141227824343034</v>
+        <v>0.08115170947598326</v>
       </c>
       <c r="C47">
-        <v>387.0848608715119</v>
+        <v>385.4487576936829</v>
       </c>
       <c r="D47">
-        <v>549.4548608715119</v>
+        <v>553.5047576936829</v>
       </c>
       <c r="E47">
-        <v>-52.53</v>
+        <v>-46.84399999999999</v>
       </c>
       <c r="F47">
-        <v>255.87</v>
+        <v>261.556</v>
       </c>
       <c r="G47">
         <v>93.5</v>
@@ -5135,28 +5135,28 @@
         <v>101.9</v>
       </c>
       <c r="M47">
-        <v>13.893741</v>
+        <v>14.2024908</v>
       </c>
       <c r="N47">
-        <v>88.006259</v>
+        <v>87.69750919999998</v>
       </c>
       <c r="O47">
-        <v>29.92212806</v>
+        <v>29.817153128</v>
       </c>
       <c r="P47">
-        <v>58.08413093999999</v>
+        <v>57.88035607199998</v>
       </c>
       <c r="Q47">
-        <v>84.18413094</v>
+        <v>83.98035607199999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1187003240789642</v>
+        <v>0.1197522768073764</v>
       </c>
       <c r="T47">
-        <v>0.9501356066118931</v>
+        <v>0.9638460771257732</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.334237769366797</v>
+        <v>7.174797817858821</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08115170947598326</v>
+        <v>0.0808911407085362</v>
       </c>
       <c r="C48">
-        <v>385.4487576936829</v>
+        <v>383.8727994186372</v>
       </c>
       <c r="D48">
-        <v>553.5047576936829</v>
+        <v>557.6147994186372</v>
       </c>
       <c r="E48">
-        <v>-46.84399999999999</v>
+        <v>-41.15800000000002</v>
       </c>
       <c r="F48">
-        <v>261.556</v>
+        <v>267.242</v>
       </c>
       <c r="G48">
         <v>93.5</v>
@@ -5217,28 +5217,28 @@
         <v>101.9</v>
       </c>
       <c r="M48">
-        <v>14.2024908</v>
+        <v>14.5112406</v>
       </c>
       <c r="N48">
-        <v>87.69750919999998</v>
+        <v>87.3887594</v>
       </c>
       <c r="O48">
-        <v>29.817153128</v>
+        <v>29.712178196</v>
       </c>
       <c r="P48">
-        <v>57.88035607199998</v>
+        <v>57.676581204</v>
       </c>
       <c r="Q48">
-        <v>83.98035607199999</v>
+        <v>83.77658120400001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1197522768073764</v>
+        <v>0.1208439258651626</v>
       </c>
       <c r="T48">
-        <v>0.9638460771257732</v>
+        <v>0.9780739238854602</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.174797817858821</v>
+        <v>7.022142545138422</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0808911407085362</v>
+        <v>0.08063057194108914</v>
       </c>
       <c r="C49">
-        <v>383.8727994186372</v>
+        <v>382.3583358849493</v>
       </c>
       <c r="D49">
-        <v>557.6147994186372</v>
+        <v>561.7863358849493</v>
       </c>
       <c r="E49">
-        <v>-41.15800000000002</v>
+        <v>-35.47199999999998</v>
       </c>
       <c r="F49">
-        <v>267.242</v>
+        <v>272.928</v>
       </c>
       <c r="G49">
         <v>93.5</v>
@@ -5299,28 +5299,28 @@
         <v>101.9</v>
       </c>
       <c r="M49">
-        <v>14.5112406</v>
+        <v>14.8199904</v>
       </c>
       <c r="N49">
-        <v>87.3887594</v>
+        <v>87.0800096</v>
       </c>
       <c r="O49">
-        <v>29.712178196</v>
+        <v>29.607203264</v>
       </c>
       <c r="P49">
-        <v>57.676581204</v>
+        <v>57.47280633599999</v>
       </c>
       <c r="Q49">
-        <v>83.77658120400001</v>
+        <v>83.572806336</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1208439258651626</v>
+        <v>0.1219775614251714</v>
       </c>
       <c r="T49">
-        <v>0.9780739238854602</v>
+        <v>0.9928489955205196</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.022142545138422</v>
+        <v>6.875847908781371</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08063057194108912</v>
+        <v>0.08037000317364207</v>
       </c>
       <c r="C50">
-        <v>382.3583358849494</v>
+        <v>380.9067576284147</v>
       </c>
       <c r="D50">
-        <v>561.7863358849494</v>
+        <v>566.0207576284147</v>
       </c>
       <c r="E50">
-        <v>-35.47200000000004</v>
+        <v>-29.786</v>
       </c>
       <c r="F50">
-        <v>272.9279999999999</v>
+        <v>278.614</v>
       </c>
       <c r="G50">
         <v>93.5</v>
@@ -5381,28 +5381,28 @@
         <v>101.9</v>
       </c>
       <c r="M50">
-        <v>14.8199904</v>
+        <v>15.1287402</v>
       </c>
       <c r="N50">
-        <v>87.0800096</v>
+        <v>86.7712598</v>
       </c>
       <c r="O50">
-        <v>29.607203264</v>
+        <v>29.502228332</v>
       </c>
       <c r="P50">
-        <v>57.47280633599999</v>
+        <v>57.26903146799999</v>
       </c>
       <c r="Q50">
-        <v>83.572806336</v>
+        <v>83.369031468</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1219775614251714</v>
+        <v>0.1231556532816511</v>
       </c>
       <c r="T50">
-        <v>0.9928489955205195</v>
+        <v>1.008203481729503</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.875847908781372</v>
+        <v>6.735524482071548</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08037000317364207</v>
+        <v>0.080109434406195</v>
       </c>
       <c r="C51">
-        <v>380.9067576284147</v>
+        <v>379.5194974274615</v>
       </c>
       <c r="D51">
-        <v>566.0207576284147</v>
+        <v>570.3194974274614</v>
       </c>
       <c r="E51">
-        <v>-29.786</v>
+        <v>-24.10000000000002</v>
       </c>
       <c r="F51">
-        <v>278.614</v>
+        <v>284.3</v>
       </c>
       <c r="G51">
         <v>93.5</v>
@@ -5463,28 +5463,28 @@
         <v>101.9</v>
       </c>
       <c r="M51">
-        <v>15.1287402</v>
+        <v>15.43749</v>
       </c>
       <c r="N51">
-        <v>86.7712598</v>
+        <v>86.46250999999999</v>
       </c>
       <c r="O51">
-        <v>29.502228332</v>
+        <v>29.3972534</v>
       </c>
       <c r="P51">
-        <v>57.26903146799999</v>
+        <v>57.0652566</v>
       </c>
       <c r="Q51">
-        <v>83.369031468</v>
+        <v>83.16525660000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1231556532816511</v>
+        <v>0.12438086881239</v>
       </c>
       <c r="T51">
-        <v>1.008203481729503</v>
+        <v>1.024172147386846</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.735524482071548</v>
+        <v>6.600813992430116</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.080109434406195</v>
+        <v>0.07984886563874795</v>
       </c>
       <c r="C52">
-        <v>379.5194974274615</v>
+        <v>378.1980319195175</v>
       </c>
       <c r="D52">
-        <v>570.3194974274614</v>
+        <v>574.6840319195175</v>
       </c>
       <c r="E52">
-        <v>-24.10000000000002</v>
+        <v>-18.41400000000004</v>
       </c>
       <c r="F52">
-        <v>284.3</v>
+        <v>289.9859999999999</v>
       </c>
       <c r="G52">
         <v>93.5</v>
@@ -5545,28 +5545,28 @@
         <v>101.9</v>
       </c>
       <c r="M52">
-        <v>15.43749</v>
+        <v>15.7462398</v>
       </c>
       <c r="N52">
-        <v>86.46250999999999</v>
+        <v>86.15376019999999</v>
       </c>
       <c r="O52">
-        <v>29.3972534</v>
+        <v>29.292278468</v>
       </c>
       <c r="P52">
-        <v>57.0652566</v>
+        <v>56.86148173199999</v>
       </c>
       <c r="Q52">
-        <v>83.16525660000001</v>
+        <v>82.96148173200001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.12438086881239</v>
+        <v>0.1256560931403019</v>
       </c>
       <c r="T52">
-        <v>1.024172147386846</v>
+        <v>1.040792595315917</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.600813992430116</v>
+        <v>6.47138626708835</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07984886563874795</v>
+        <v>0.07958829687130087</v>
       </c>
       <c r="C53">
-        <v>378.1980319195175</v>
+        <v>376.9438832921737</v>
       </c>
       <c r="D53">
-        <v>574.6840319195175</v>
+        <v>579.1158832921736</v>
       </c>
       <c r="E53">
-        <v>-18.41400000000004</v>
+        <v>-12.72800000000001</v>
       </c>
       <c r="F53">
-        <v>289.9859999999999</v>
+        <v>295.672</v>
       </c>
       <c r="G53">
         <v>93.5</v>
@@ -5627,28 +5627,28 @@
         <v>101.9</v>
       </c>
       <c r="M53">
-        <v>15.7462398</v>
+        <v>16.0549896</v>
       </c>
       <c r="N53">
-        <v>86.15376019999999</v>
+        <v>85.84501039999999</v>
       </c>
       <c r="O53">
-        <v>29.292278468</v>
+        <v>29.187303536</v>
       </c>
       <c r="P53">
-        <v>56.86148173199999</v>
+        <v>56.65770686399999</v>
       </c>
       <c r="Q53">
-        <v>82.96148173200001</v>
+        <v>82.757706864</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1256560931403019</v>
+        <v>0.1269844518152101</v>
       </c>
       <c r="T53">
-        <v>1.040792595315917</v>
+        <v>1.058105561908699</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.47138626708835</v>
+        <v>6.346936531182804</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07958829687130087</v>
+        <v>0.0793277281038538</v>
       </c>
       <c r="C54">
-        <v>376.9438832921737</v>
+        <v>375.7586210532006</v>
       </c>
       <c r="D54">
-        <v>579.1158832921736</v>
+        <v>583.6166210532006</v>
       </c>
       <c r="E54">
-        <v>-12.72800000000001</v>
+        <v>-7.04200000000003</v>
       </c>
       <c r="F54">
-        <v>295.672</v>
+        <v>301.3579999999999</v>
       </c>
       <c r="G54">
         <v>93.5</v>
@@ -5709,28 +5709,28 @@
         <v>101.9</v>
       </c>
       <c r="M54">
-        <v>16.0549896</v>
+        <v>16.3637394</v>
       </c>
       <c r="N54">
-        <v>85.84501039999999</v>
+        <v>85.53626059999999</v>
       </c>
       <c r="O54">
-        <v>29.187303536</v>
+        <v>29.082328604</v>
       </c>
       <c r="P54">
-        <v>56.65770686399999</v>
+        <v>56.45393199599999</v>
       </c>
       <c r="Q54">
-        <v>82.757706864</v>
+        <v>82.553931996</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1269844518152101</v>
+        <v>0.1283693363911783</v>
       </c>
       <c r="T54">
-        <v>1.058105561908699</v>
+        <v>1.076155250484153</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.346936531182804</v>
+        <v>6.227183011726526</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0793277281038538</v>
+        <v>0.07906715933640673</v>
       </c>
       <c r="C55">
-        <v>375.7586210532006</v>
+        <v>374.6438638837549</v>
       </c>
       <c r="D55">
-        <v>583.6166210532006</v>
+        <v>588.1878638837549</v>
       </c>
       <c r="E55">
-        <v>-7.04200000000003</v>
+        <v>-1.355999999999995</v>
       </c>
       <c r="F55">
-        <v>301.3579999999999</v>
+        <v>307.044</v>
       </c>
       <c r="G55">
         <v>93.5</v>
@@ -5791,28 +5791,28 @@
         <v>101.9</v>
       </c>
       <c r="M55">
-        <v>16.3637394</v>
+        <v>16.6724892</v>
       </c>
       <c r="N55">
-        <v>85.53626059999999</v>
+        <v>85.22751079999999</v>
       </c>
       <c r="O55">
-        <v>29.082328604</v>
+        <v>28.977353672</v>
       </c>
       <c r="P55">
-        <v>56.45393199599999</v>
+        <v>56.25015712799999</v>
       </c>
       <c r="Q55">
-        <v>82.553931996</v>
+        <v>82.35015712800001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1283693363911783</v>
+        <v>0.1298144333400147</v>
       </c>
       <c r="T55">
-        <v>1.076155250484153</v>
+        <v>1.094989708128105</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.227183011726526</v>
+        <v>6.111864807805663</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07906715933640673</v>
+        <v>0.07916959056895967</v>
       </c>
       <c r="C56">
-        <v>374.6438638837549</v>
+        <v>367.1523635212081</v>
       </c>
       <c r="D56">
-        <v>588.1878638837549</v>
+        <v>586.382363521208</v>
       </c>
       <c r="E56">
-        <v>-1.355999999999995</v>
+        <v>4.329999999999984</v>
       </c>
       <c r="F56">
-        <v>307.044</v>
+        <v>312.73</v>
       </c>
       <c r="G56">
         <v>93.5</v>
@@ -5873,45 +5873,45 @@
         <v>101.9</v>
       </c>
       <c r="M56">
-        <v>16.6724892</v>
+        <v>17.293969</v>
       </c>
       <c r="N56">
-        <v>85.22751079999999</v>
+        <v>84.606031</v>
       </c>
       <c r="O56">
-        <v>28.977353672</v>
+        <v>28.76605054</v>
       </c>
       <c r="P56">
-        <v>56.25015712799999</v>
+        <v>55.83998046</v>
       </c>
       <c r="Q56">
-        <v>82.35015712800001</v>
+        <v>81.93998046000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1298144333400147</v>
+        <v>0.1313237568199104</v>
       </c>
       <c r="T56">
-        <v>1.094989708128105</v>
+        <v>1.114661252778455</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.34</v>
       </c>
       <c r="W56">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.111864807805663</v>
+        <v>5.89222751584671</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07916959056895967</v>
+        <v>0.07891562180151261</v>
       </c>
       <c r="C57">
-        <v>367.1523635212081</v>
+        <v>365.9634195332855</v>
       </c>
       <c r="D57">
-        <v>586.382363521208</v>
+        <v>590.8794195332855</v>
       </c>
       <c r="E57">
-        <v>4.329999999999984</v>
+        <v>10.01600000000002</v>
       </c>
       <c r="F57">
-        <v>312.73</v>
+        <v>318.416</v>
       </c>
       <c r="G57">
         <v>93.5</v>
@@ -5955,28 +5955,28 @@
         <v>101.9</v>
       </c>
       <c r="M57">
-        <v>17.293969</v>
+        <v>17.6084048</v>
       </c>
       <c r="N57">
-        <v>84.606031</v>
+        <v>84.29159519999999</v>
       </c>
       <c r="O57">
-        <v>28.76605054</v>
+        <v>28.659142368</v>
       </c>
       <c r="P57">
-        <v>55.83998046</v>
+        <v>55.63245283199999</v>
       </c>
       <c r="Q57">
-        <v>81.93998046000002</v>
+        <v>81.73245283200001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1313237568199104</v>
+        <v>0.1329016859125287</v>
       </c>
       <c r="T57">
-        <v>1.114661252778455</v>
+        <v>1.135226958549275</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.89222751584671</v>
+        <v>5.787009167349447</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07891562180151261</v>
+        <v>0.07866165303406555</v>
       </c>
       <c r="C58">
-        <v>365.9634195332855</v>
+        <v>364.8439858509671</v>
       </c>
       <c r="D58">
-        <v>590.8794195332855</v>
+        <v>595.4459858509671</v>
       </c>
       <c r="E58">
-        <v>10.01600000000002</v>
+        <v>15.702</v>
       </c>
       <c r="F58">
-        <v>318.416</v>
+        <v>324.102</v>
       </c>
       <c r="G58">
         <v>93.5</v>
@@ -6037,28 +6037,28 @@
         <v>101.9</v>
       </c>
       <c r="M58">
-        <v>17.6084048</v>
+        <v>17.9228406</v>
       </c>
       <c r="N58">
-        <v>84.29159519999999</v>
+        <v>83.97715939999999</v>
       </c>
       <c r="O58">
-        <v>28.659142368</v>
+        <v>28.552234196</v>
       </c>
       <c r="P58">
-        <v>55.63245283199999</v>
+        <v>55.42492520399999</v>
       </c>
       <c r="Q58">
-        <v>81.73245283200001</v>
+        <v>81.524925204</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1329016859125287</v>
+        <v>0.1345530070559664</v>
       </c>
       <c r="T58">
-        <v>1.135226958549275</v>
+        <v>1.156749208774552</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.787009167349447</v>
+        <v>5.68548269072928</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07866165303406555</v>
+        <v>0.07840768426661848</v>
       </c>
       <c r="C59">
-        <v>364.8439858509671</v>
+        <v>363.7956866417187</v>
       </c>
       <c r="D59">
-        <v>595.4459858509671</v>
+        <v>600.0836866417187</v>
       </c>
       <c r="E59">
-        <v>15.702</v>
+        <v>21.38800000000003</v>
       </c>
       <c r="F59">
-        <v>324.102</v>
+        <v>329.788</v>
       </c>
       <c r="G59">
         <v>93.5</v>
@@ -6119,28 +6119,28 @@
         <v>101.9</v>
       </c>
       <c r="M59">
-        <v>17.9228406</v>
+        <v>18.2372764</v>
       </c>
       <c r="N59">
-        <v>83.97715939999999</v>
+        <v>83.66272359999999</v>
       </c>
       <c r="O59">
-        <v>28.552234196</v>
+        <v>28.445326024</v>
       </c>
       <c r="P59">
-        <v>55.42492520399999</v>
+        <v>55.217397576</v>
       </c>
       <c r="Q59">
-        <v>81.524925204</v>
+        <v>81.317397576</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1345530070559664</v>
+        <v>0.1362829625395678</v>
       </c>
       <c r="T59">
-        <v>1.156749208774552</v>
+        <v>1.179296328058175</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.68548269072928</v>
+        <v>5.587457127096016</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07840768426661848</v>
+        <v>0.07815371549917141</v>
       </c>
       <c r="C60">
-        <v>363.7956866417188</v>
+        <v>362.8201970702781</v>
       </c>
       <c r="D60">
-        <v>600.0836866417187</v>
+        <v>604.7941970702781</v>
       </c>
       <c r="E60">
-        <v>21.38799999999992</v>
+        <v>27.07399999999996</v>
       </c>
       <c r="F60">
-        <v>329.7879999999999</v>
+        <v>335.4739999999999</v>
       </c>
       <c r="G60">
         <v>93.5</v>
@@ -6201,28 +6201,28 @@
         <v>101.9</v>
       </c>
       <c r="M60">
-        <v>18.2372764</v>
+        <v>18.5517122</v>
       </c>
       <c r="N60">
-        <v>83.66272359999999</v>
+        <v>83.34828779999999</v>
       </c>
       <c r="O60">
-        <v>28.445326024</v>
+        <v>28.338417852</v>
       </c>
       <c r="P60">
-        <v>55.217397576</v>
+        <v>55.009869948</v>
       </c>
       <c r="Q60">
-        <v>81.317397576</v>
+        <v>81.10986994800001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1362829625395678</v>
+        <v>0.1380973060955401</v>
       </c>
       <c r="T60">
-        <v>1.179296328058175</v>
+        <v>1.202943306819048</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.587457127096018</v>
+        <v>5.492754463924899</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07815371549917141</v>
+        <v>0.07789974673172435</v>
       </c>
       <c r="C61">
-        <v>362.8201970702781</v>
+        <v>361.9192453160724</v>
       </c>
       <c r="D61">
-        <v>604.7941970702781</v>
+        <v>609.5792453160723</v>
       </c>
       <c r="E61">
-        <v>27.07399999999996</v>
+        <v>32.75999999999993</v>
       </c>
       <c r="F61">
-        <v>335.4739999999999</v>
+        <v>341.1599999999999</v>
       </c>
       <c r="G61">
         <v>93.5</v>
@@ -6283,28 +6283,28 @@
         <v>101.9</v>
       </c>
       <c r="M61">
-        <v>18.5517122</v>
+        <v>18.866148</v>
       </c>
       <c r="N61">
-        <v>83.34828779999999</v>
+        <v>83.033852</v>
       </c>
       <c r="O61">
-        <v>28.338417852</v>
+        <v>28.23150968</v>
       </c>
       <c r="P61">
-        <v>55.009869948</v>
+        <v>54.80234231999999</v>
       </c>
       <c r="Q61">
-        <v>81.10986994800001</v>
+        <v>80.90234232</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1380973060955401</v>
+        <v>0.1400023668293109</v>
       </c>
       <c r="T61">
-        <v>1.202943306819048</v>
+        <v>1.227772634517966</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.492754463924899</v>
+        <v>5.401208556192818</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07789974673172435</v>
+        <v>0.0776457779642773</v>
       </c>
       <c r="C62">
-        <v>361.9192453160724</v>
+        <v>361.0946146871673</v>
       </c>
       <c r="D62">
-        <v>609.5792453160723</v>
+        <v>614.4406146871672</v>
       </c>
       <c r="E62">
-        <v>32.75999999999993</v>
+        <v>38.44599999999997</v>
       </c>
       <c r="F62">
-        <v>341.1599999999999</v>
+        <v>346.8459999999999</v>
       </c>
       <c r="G62">
         <v>93.5</v>
@@ -6365,28 +6365,28 @@
         <v>101.9</v>
       </c>
       <c r="M62">
-        <v>18.866148</v>
+        <v>19.1805838</v>
       </c>
       <c r="N62">
-        <v>83.033852</v>
+        <v>82.7194162</v>
       </c>
       <c r="O62">
-        <v>28.23150968</v>
+        <v>28.124601508</v>
       </c>
       <c r="P62">
-        <v>54.80234231999999</v>
+        <v>54.594814692</v>
       </c>
       <c r="Q62">
-        <v>80.90234232</v>
+        <v>80.69481469200001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1400023668293109</v>
+        <v>0.1420051229853264</v>
       </c>
       <c r="T62">
-        <v>1.227772634517966</v>
+        <v>1.253875261073238</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.401208556192818</v>
+        <v>5.312664153632279</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0776457779642773</v>
+        <v>0.07739180919683022</v>
       </c>
       <c r="C63">
-        <v>361.0946146871673</v>
+        <v>360.3481458361836</v>
       </c>
       <c r="D63">
-        <v>614.4406146871672</v>
+        <v>619.3801458361835</v>
       </c>
       <c r="E63">
-        <v>38.44599999999997</v>
+        <v>44.13199999999995</v>
       </c>
       <c r="F63">
-        <v>346.8459999999999</v>
+        <v>352.5319999999999</v>
       </c>
       <c r="G63">
         <v>93.5</v>
@@ -6447,28 +6447,28 @@
         <v>101.9</v>
       </c>
       <c r="M63">
-        <v>19.1805838</v>
+        <v>19.4950196</v>
       </c>
       <c r="N63">
-        <v>82.7194162</v>
+        <v>82.4049804</v>
       </c>
       <c r="O63">
-        <v>28.124601508</v>
+        <v>28.017693336</v>
       </c>
       <c r="P63">
-        <v>54.594814692</v>
+        <v>54.387287064</v>
       </c>
       <c r="Q63">
-        <v>80.69481469200001</v>
+        <v>80.48728706400001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1420051229853264</v>
+        <v>0.1441132873600796</v>
       </c>
       <c r="T63">
-        <v>1.253875261073238</v>
+        <v>1.281351710078787</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.312664153632279</v>
+        <v>5.226976022122082</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07739180919683022</v>
+        <v>0.07713784042938318</v>
       </c>
       <c r="C64">
-        <v>360.3481458361836</v>
+        <v>359.6817390839586</v>
       </c>
       <c r="D64">
-        <v>619.3801458361835</v>
+        <v>624.3997390839586</v>
       </c>
       <c r="E64">
-        <v>44.13199999999995</v>
+        <v>49.81799999999998</v>
       </c>
       <c r="F64">
-        <v>352.5319999999999</v>
+        <v>358.218</v>
       </c>
       <c r="G64">
         <v>93.5</v>
@@ -6529,28 +6529,28 @@
         <v>101.9</v>
       </c>
       <c r="M64">
-        <v>19.4950196</v>
+        <v>19.8094554</v>
       </c>
       <c r="N64">
-        <v>82.4049804</v>
+        <v>82.09054459999999</v>
       </c>
       <c r="O64">
-        <v>28.017693336</v>
+        <v>27.910785164</v>
       </c>
       <c r="P64">
-        <v>54.387287064</v>
+        <v>54.17975943599999</v>
       </c>
       <c r="Q64">
-        <v>80.48728706400001</v>
+        <v>80.27975943600001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1441132873600796</v>
+        <v>0.1463354065659005</v>
       </c>
       <c r="T64">
-        <v>1.281351710078787</v>
+        <v>1.310313372544095</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.226976022122082</v>
+        <v>5.144008148755064</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07713784042938318</v>
+        <v>0.07688387166193611</v>
       </c>
       <c r="C65">
-        <v>359.6817390839586</v>
+        <v>359.0973568571273</v>
       </c>
       <c r="D65">
-        <v>624.3997390839586</v>
+        <v>629.5013568571272</v>
       </c>
       <c r="E65">
-        <v>49.81799999999998</v>
+        <v>55.50399999999996</v>
       </c>
       <c r="F65">
-        <v>358.218</v>
+        <v>363.9039999999999</v>
       </c>
       <c r="G65">
         <v>93.5</v>
@@ -6611,28 +6611,28 @@
         <v>101.9</v>
       </c>
       <c r="M65">
-        <v>19.8094554</v>
+        <v>20.1238912</v>
       </c>
       <c r="N65">
-        <v>82.09054459999999</v>
+        <v>81.7761088</v>
       </c>
       <c r="O65">
-        <v>27.910785164</v>
+        <v>27.803876992</v>
       </c>
       <c r="P65">
-        <v>54.17975943599999</v>
+        <v>53.972231808</v>
       </c>
       <c r="Q65">
-        <v>80.27975943600001</v>
+        <v>80.07223180800001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1463354065659005</v>
+        <v>0.1486809768387114</v>
       </c>
       <c r="T65">
-        <v>1.310313372544095</v>
+        <v>1.340884016257477</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.144008148755064</v>
+        <v>5.063633021430767</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07688387166193611</v>
+        <v>0.07662990289448904</v>
       </c>
       <c r="C66">
-        <v>359.0973568571273</v>
+        <v>358.5970262461748</v>
       </c>
       <c r="D66">
-        <v>629.5013568571272</v>
+        <v>634.6870262461748</v>
       </c>
       <c r="E66">
-        <v>55.50399999999996</v>
+        <v>61.19</v>
       </c>
       <c r="F66">
-        <v>363.9039999999999</v>
+        <v>369.59</v>
       </c>
       <c r="G66">
         <v>93.5</v>
@@ -6693,28 +6693,28 @@
         <v>101.9</v>
       </c>
       <c r="M66">
-        <v>20.1238912</v>
+        <v>20.438327</v>
       </c>
       <c r="N66">
-        <v>81.7761088</v>
+        <v>81.46167299999999</v>
       </c>
       <c r="O66">
-        <v>27.803876992</v>
+        <v>27.69696882</v>
       </c>
       <c r="P66">
-        <v>53.972231808</v>
+        <v>53.76470418</v>
       </c>
       <c r="Q66">
-        <v>80.07223180800001</v>
+        <v>79.86470418</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1486809768387114</v>
+        <v>0.1511605796985401</v>
       </c>
       <c r="T66">
-        <v>1.340884016257477</v>
+        <v>1.373201553897337</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.063633021430767</v>
+        <v>4.985730974947215</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07662990289448904</v>
+        <v>0.07637593412704197</v>
       </c>
       <c r="C67">
-        <v>358.5970262461748</v>
+        <v>358.1828416909834</v>
       </c>
       <c r="D67">
-        <v>634.6870262461748</v>
+        <v>639.9588416909834</v>
       </c>
       <c r="E67">
-        <v>61.19</v>
+        <v>66.87599999999998</v>
       </c>
       <c r="F67">
-        <v>369.59</v>
+        <v>375.276</v>
       </c>
       <c r="G67">
         <v>93.5</v>
@@ -6775,28 +6775,28 @@
         <v>101.9</v>
       </c>
       <c r="M67">
-        <v>20.438327</v>
+        <v>20.7527628</v>
       </c>
       <c r="N67">
-        <v>81.46167299999999</v>
+        <v>81.14723719999999</v>
       </c>
       <c r="O67">
-        <v>27.69696882</v>
+        <v>27.590060648</v>
       </c>
       <c r="P67">
-        <v>53.76470418</v>
+        <v>53.55717655199999</v>
       </c>
       <c r="Q67">
-        <v>79.86470418</v>
+        <v>79.65717655200001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1511605796985401</v>
+        <v>0.1537860415501235</v>
       </c>
       <c r="T67">
-        <v>1.373201553897337</v>
+        <v>1.407420123163072</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.985730974947215</v>
+        <v>4.910189596538924</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07637593412704197</v>
+        <v>0.07612196535959491</v>
       </c>
       <c r="C68">
-        <v>358.1828416909834</v>
+        <v>357.8569678013338</v>
       </c>
       <c r="D68">
-        <v>639.9588416909834</v>
+        <v>645.3189678013338</v>
       </c>
       <c r="E68">
-        <v>66.87599999999998</v>
+        <v>72.56200000000001</v>
       </c>
       <c r="F68">
-        <v>375.276</v>
+        <v>380.962</v>
       </c>
       <c r="G68">
         <v>93.5</v>
@@ -6857,28 +6857,28 @@
         <v>101.9</v>
       </c>
       <c r="M68">
-        <v>20.7527628</v>
+        <v>21.0671986</v>
       </c>
       <c r="N68">
-        <v>81.14723719999999</v>
+        <v>80.83280139999999</v>
       </c>
       <c r="O68">
-        <v>27.590060648</v>
+        <v>27.483152476</v>
       </c>
       <c r="P68">
-        <v>53.55717655199999</v>
+        <v>53.34964892399999</v>
       </c>
       <c r="Q68">
-        <v>79.65717655200001</v>
+        <v>79.449648924</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1537860415501235</v>
+        <v>0.1565706223018028</v>
       </c>
       <c r="T68">
-        <v>1.407420123163072</v>
+        <v>1.443712545111578</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.910189596538924</v>
+        <v>4.836903184650284</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07612196535959491</v>
+        <v>0.07586799659214784</v>
       </c>
       <c r="C69">
-        <v>357.8569678013338</v>
+        <v>357.6216423203512</v>
       </c>
       <c r="D69">
-        <v>645.3189678013338</v>
+        <v>650.7696423203512</v>
       </c>
       <c r="E69">
-        <v>72.56200000000001</v>
+        <v>78.24799999999999</v>
       </c>
       <c r="F69">
-        <v>380.962</v>
+        <v>386.648</v>
       </c>
       <c r="G69">
         <v>93.5</v>
@@ -6939,28 +6939,28 @@
         <v>101.9</v>
       </c>
       <c r="M69">
-        <v>21.0671986</v>
+        <v>21.3816344</v>
       </c>
       <c r="N69">
-        <v>80.83280139999999</v>
+        <v>80.5183656</v>
       </c>
       <c r="O69">
-        <v>27.483152476</v>
+        <v>27.376244304</v>
       </c>
       <c r="P69">
-        <v>53.34964892399999</v>
+        <v>53.142121296</v>
       </c>
       <c r="Q69">
-        <v>79.449648924</v>
+        <v>79.24212129600001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1565706223018028</v>
+        <v>0.159529239350462</v>
       </c>
       <c r="T69">
-        <v>1.443712545111578</v>
+        <v>1.482273243431866</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.836903184650284</v>
+        <v>4.765772255464251</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07586799659214784</v>
+        <v>0.07561402782470078</v>
       </c>
       <c r="C70">
-        <v>357.6216423203512</v>
+        <v>357.4791792394096</v>
       </c>
       <c r="D70">
-        <v>650.7696423203512</v>
+        <v>656.3131792394096</v>
       </c>
       <c r="E70">
-        <v>78.24799999999999</v>
+        <v>83.93399999999997</v>
       </c>
       <c r="F70">
-        <v>386.648</v>
+        <v>392.3339999999999</v>
       </c>
       <c r="G70">
         <v>93.5</v>
@@ -7021,28 +7021,28 @@
         <v>101.9</v>
       </c>
       <c r="M70">
-        <v>21.3816344</v>
+        <v>21.6960702</v>
       </c>
       <c r="N70">
-        <v>80.5183656</v>
+        <v>80.2039298</v>
       </c>
       <c r="O70">
-        <v>27.376244304</v>
+        <v>27.269336132</v>
       </c>
       <c r="P70">
-        <v>53.142121296</v>
+        <v>52.934593668</v>
       </c>
       <c r="Q70">
-        <v>79.24212129600001</v>
+        <v>79.03459366800001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.159529239350462</v>
+        <v>0.1626787349183897</v>
       </c>
       <c r="T70">
-        <v>1.482273243431866</v>
+        <v>1.523321728740559</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.765772255464251</v>
+        <v>4.69670309234158</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07561402782470078</v>
+        <v>0.07536005905725372</v>
       </c>
       <c r="C71">
-        <v>357.4791792394096</v>
+        <v>357.4319720736137</v>
       </c>
       <c r="D71">
-        <v>656.3131792394096</v>
+        <v>661.9519720736137</v>
       </c>
       <c r="E71">
-        <v>83.93399999999997</v>
+        <v>89.62</v>
       </c>
       <c r="F71">
-        <v>392.3339999999999</v>
+        <v>398.02</v>
       </c>
       <c r="G71">
         <v>93.5</v>
@@ -7103,28 +7103,28 @@
         <v>101.9</v>
       </c>
       <c r="M71">
-        <v>21.6960702</v>
+        <v>22.010506</v>
       </c>
       <c r="N71">
-        <v>80.2039298</v>
+        <v>79.88949399999998</v>
       </c>
       <c r="O71">
-        <v>27.269336132</v>
+        <v>27.16242796</v>
       </c>
       <c r="P71">
-        <v>52.934593668</v>
+        <v>52.72706603999999</v>
       </c>
       <c r="Q71">
-        <v>79.03459366800001</v>
+        <v>78.82706604000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1626787349183897</v>
+        <v>0.1660381968575124</v>
       </c>
       <c r="T71">
-        <v>1.523321728740559</v>
+        <v>1.567106779736499</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.69670309234158</v>
+        <v>4.629607333879557</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07536005905725372</v>
+        <v>0.07510609028980665</v>
       </c>
       <c r="C72">
-        <v>357.4319720736137</v>
+        <v>357.482497307591</v>
       </c>
       <c r="D72">
-        <v>661.9519720736137</v>
+        <v>667.688497307591</v>
       </c>
       <c r="E72">
-        <v>89.62</v>
+        <v>95.30599999999998</v>
       </c>
       <c r="F72">
-        <v>398.02</v>
+        <v>403.706</v>
       </c>
       <c r="G72">
         <v>93.5</v>
@@ -7185,28 +7185,28 @@
         <v>101.9</v>
       </c>
       <c r="M72">
-        <v>22.010506</v>
+        <v>22.3249418</v>
       </c>
       <c r="N72">
-        <v>79.88949399999998</v>
+        <v>79.5750582</v>
       </c>
       <c r="O72">
-        <v>27.16242796</v>
+        <v>27.055519788</v>
       </c>
       <c r="P72">
-        <v>52.72706603999999</v>
+        <v>52.519538412</v>
       </c>
       <c r="Q72">
-        <v>78.82706604000001</v>
+        <v>78.61953841200001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1660381968575124</v>
+        <v>0.1696293458269195</v>
       </c>
       <c r="T72">
-        <v>1.567106779736499</v>
+        <v>1.613911489421814</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.629607333879557</v>
+        <v>4.564401596782663</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07510609028980665</v>
+        <v>0.07485212152235959</v>
       </c>
       <c r="C73">
-        <v>357.4824973075911</v>
+        <v>357.633318022019</v>
       </c>
       <c r="D73">
-        <v>667.688497307591</v>
+        <v>673.525318022019</v>
       </c>
       <c r="E73">
-        <v>95.30599999999993</v>
+        <v>100.992</v>
       </c>
       <c r="F73">
-        <v>403.7059999999999</v>
+        <v>409.3919999999999</v>
       </c>
       <c r="G73">
         <v>93.5</v>
@@ -7267,28 +7267,28 @@
         <v>101.9</v>
       </c>
       <c r="M73">
-        <v>22.32494179999999</v>
+        <v>22.6393776</v>
       </c>
       <c r="N73">
-        <v>79.5750582</v>
+        <v>79.26062239999999</v>
       </c>
       <c r="O73">
-        <v>27.055519788</v>
+        <v>26.948611616</v>
       </c>
       <c r="P73">
-        <v>52.519538412</v>
+        <v>52.31201078399999</v>
       </c>
       <c r="Q73">
-        <v>78.61953841200001</v>
+        <v>78.412010784</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1696293458269195</v>
+        <v>0.1734770054369985</v>
       </c>
       <c r="T73">
-        <v>1.613911489421814</v>
+        <v>1.66405939265608</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.564401596782663</v>
+        <v>4.501007130160681</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07485212152235959</v>
+        <v>0.07580265275491253</v>
       </c>
       <c r="C74">
-        <v>357.633318022019</v>
+        <v>330.6089765118587</v>
       </c>
       <c r="D74">
-        <v>673.525318022019</v>
+        <v>652.1869765118586</v>
       </c>
       <c r="E74">
-        <v>100.992</v>
+        <v>106.6779999999999</v>
       </c>
       <c r="F74">
-        <v>409.3919999999999</v>
+        <v>415.0779999999999</v>
       </c>
       <c r="G74">
         <v>93.5</v>
@@ -7349,45 +7349,45 @@
         <v>101.9</v>
       </c>
       <c r="M74">
-        <v>22.6393776</v>
+        <v>23.9915084</v>
       </c>
       <c r="N74">
-        <v>79.26062239999999</v>
+        <v>77.90849159999999</v>
       </c>
       <c r="O74">
-        <v>26.948611616</v>
+        <v>26.488887144</v>
       </c>
       <c r="P74">
-        <v>52.31201078399999</v>
+        <v>51.41960445599999</v>
       </c>
       <c r="Q74">
-        <v>78.412010784</v>
+        <v>77.519604456</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1734770054369985</v>
+        <v>0.1776096768700464</v>
       </c>
       <c r="T74">
-        <v>1.66405939265608</v>
+        <v>1.71792195538918</v>
       </c>
       <c r="U74">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V74">
         <v>0.34</v>
       </c>
       <c r="W74">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.501007130160681</v>
+        <v>4.247336111638566</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07580265275491253</v>
+        <v>0.07556518398746546</v>
       </c>
       <c r="C75">
-        <v>330.6089765118587</v>
+        <v>330.126170872173</v>
       </c>
       <c r="D75">
-        <v>652.1869765118586</v>
+        <v>657.3901708721729</v>
       </c>
       <c r="E75">
-        <v>106.6779999999999</v>
+        <v>112.364</v>
       </c>
       <c r="F75">
-        <v>415.0779999999999</v>
+        <v>420.764</v>
       </c>
       <c r="G75">
         <v>93.5</v>
@@ -7431,28 +7431,28 @@
         <v>101.9</v>
       </c>
       <c r="M75">
-        <v>23.9915084</v>
+        <v>24.3201592</v>
       </c>
       <c r="N75">
-        <v>77.90849159999999</v>
+        <v>77.5798408</v>
       </c>
       <c r="O75">
-        <v>26.488887144</v>
+        <v>26.377145872</v>
       </c>
       <c r="P75">
-        <v>51.41960445599999</v>
+        <v>51.202694928</v>
       </c>
       <c r="Q75">
-        <v>77.519604456</v>
+        <v>77.30269492800001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1776096768700464</v>
+        <v>0.1820602461056364</v>
       </c>
       <c r="T75">
-        <v>1.71792195538918</v>
+        <v>1.775927792178673</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.247336111638566</v>
+        <v>4.189939677697504</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07556518398746546</v>
+        <v>0.0753277152200184</v>
       </c>
       <c r="C76">
-        <v>330.126170872173</v>
+        <v>329.7270558358629</v>
       </c>
       <c r="D76">
-        <v>657.3901708721729</v>
+        <v>662.6770558358628</v>
       </c>
       <c r="E76">
-        <v>112.364</v>
+        <v>118.05</v>
       </c>
       <c r="F76">
-        <v>420.764</v>
+        <v>426.4499999999999</v>
       </c>
       <c r="G76">
         <v>93.5</v>
@@ -7513,28 +7513,28 @@
         <v>101.9</v>
       </c>
       <c r="M76">
-        <v>24.3201592</v>
+        <v>24.64881</v>
       </c>
       <c r="N76">
-        <v>77.5798408</v>
+        <v>77.25118999999999</v>
       </c>
       <c r="O76">
-        <v>26.377145872</v>
+        <v>26.2654046</v>
       </c>
       <c r="P76">
-        <v>51.202694928</v>
+        <v>50.9857854</v>
       </c>
       <c r="Q76">
-        <v>77.30269492800001</v>
+        <v>77.08578540000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1820602461056364</v>
+        <v>0.1868668608800736</v>
       </c>
       <c r="T76">
-        <v>1.775927792178673</v>
+        <v>1.838574095911325</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.189939677697504</v>
+        <v>4.134073815328204</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0753277152200184</v>
+        <v>0.07509024645257134</v>
       </c>
       <c r="C77">
-        <v>329.7270558358629</v>
+        <v>329.4136669512935</v>
       </c>
       <c r="D77">
-        <v>662.6770558358628</v>
+        <v>668.0496669512934</v>
       </c>
       <c r="E77">
-        <v>118.05</v>
+        <v>123.7359999999999</v>
       </c>
       <c r="F77">
-        <v>426.4499999999999</v>
+        <v>432.1359999999999</v>
       </c>
       <c r="G77">
         <v>93.5</v>
@@ -7595,28 +7595,28 @@
         <v>101.9</v>
       </c>
       <c r="M77">
-        <v>24.64881</v>
+        <v>24.9774608</v>
       </c>
       <c r="N77">
-        <v>77.25118999999999</v>
+        <v>76.92253919999999</v>
       </c>
       <c r="O77">
-        <v>26.2654046</v>
+        <v>26.153663328</v>
       </c>
       <c r="P77">
-        <v>50.9857854</v>
+        <v>50.768875872</v>
       </c>
       <c r="Q77">
-        <v>77.08578540000001</v>
+        <v>76.868875872</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1868668608800736</v>
+        <v>0.1920740268857139</v>
       </c>
       <c r="T77">
-        <v>1.838574095911325</v>
+        <v>1.906440924955032</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.134073815328204</v>
+        <v>4.07967810723178</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07509024645257134</v>
+        <v>0.07485277768512427</v>
       </c>
       <c r="C78">
-        <v>329.4136669512935</v>
+        <v>329.1881063186995</v>
       </c>
       <c r="D78">
-        <v>668.0496669512934</v>
+        <v>673.5101063186994</v>
       </c>
       <c r="E78">
-        <v>123.7359999999999</v>
+        <v>129.422</v>
       </c>
       <c r="F78">
-        <v>432.1359999999999</v>
+        <v>437.8219999999999</v>
       </c>
       <c r="G78">
         <v>93.5</v>
@@ -7677,28 +7677,28 @@
         <v>101.9</v>
       </c>
       <c r="M78">
-        <v>24.9774608</v>
+        <v>25.3061116</v>
       </c>
       <c r="N78">
-        <v>76.92253919999999</v>
+        <v>76.5938884</v>
       </c>
       <c r="O78">
-        <v>26.153663328</v>
+        <v>26.041922056</v>
       </c>
       <c r="P78">
-        <v>50.768875872</v>
+        <v>50.55196634399999</v>
       </c>
       <c r="Q78">
-        <v>76.868875872</v>
+        <v>76.651966344</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1920740268857139</v>
+        <v>0.1977339899353229</v>
       </c>
       <c r="T78">
-        <v>1.906440924955032</v>
+        <v>1.980209217393844</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.07967810723178</v>
+        <v>4.026695274670329</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07485277768512427</v>
+        <v>0.07641710891767721</v>
       </c>
       <c r="C79">
-        <v>329.1881063186995</v>
+        <v>289.09020617531</v>
       </c>
       <c r="D79">
-        <v>673.5101063186994</v>
+        <v>639.0982061753099</v>
       </c>
       <c r="E79">
-        <v>129.422</v>
+        <v>135.1079999999999</v>
       </c>
       <c r="F79">
-        <v>437.8219999999999</v>
+        <v>443.5079999999999</v>
       </c>
       <c r="G79">
         <v>93.5</v>
@@ -7759,45 +7759,45 @@
         <v>101.9</v>
       </c>
       <c r="M79">
-        <v>25.3061116</v>
+        <v>27.1870404</v>
       </c>
       <c r="N79">
-        <v>76.5938884</v>
+        <v>74.71295959999999</v>
       </c>
       <c r="O79">
-        <v>26.041922056</v>
+        <v>25.402406264</v>
       </c>
       <c r="P79">
-        <v>50.55196634399999</v>
+        <v>49.31055333599999</v>
       </c>
       <c r="Q79">
-        <v>76.651966344</v>
+        <v>75.41055333599999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1977339899353229</v>
+        <v>0.203908495080351</v>
       </c>
       <c r="T79">
-        <v>1.980209217393844</v>
+        <v>2.060683718236184</v>
       </c>
       <c r="U79">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V79">
         <v>0.34</v>
       </c>
       <c r="W79">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>4.026695274670329</v>
+        <v>3.74810933815363</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07641710891767721</v>
+        <v>0.07620274015023015</v>
       </c>
       <c r="C80">
-        <v>289.09020617531</v>
+        <v>287.9104675865659</v>
       </c>
       <c r="D80">
-        <v>639.0982061753099</v>
+        <v>643.6044675865659</v>
       </c>
       <c r="E80">
-        <v>135.1079999999999</v>
+        <v>140.794</v>
       </c>
       <c r="F80">
-        <v>443.5079999999999</v>
+        <v>449.194</v>
       </c>
       <c r="G80">
         <v>93.5</v>
@@ -7841,28 +7841,28 @@
         <v>101.9</v>
       </c>
       <c r="M80">
-        <v>27.1870404</v>
+        <v>27.5355922</v>
       </c>
       <c r="N80">
-        <v>74.71295959999999</v>
+        <v>74.3644078</v>
       </c>
       <c r="O80">
-        <v>25.402406264</v>
+        <v>25.283898652</v>
       </c>
       <c r="P80">
-        <v>49.31055333599999</v>
+        <v>49.08050914799999</v>
       </c>
       <c r="Q80">
-        <v>75.41055333599999</v>
+        <v>75.180509148</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.203908495080351</v>
+        <v>0.2106710483344293</v>
       </c>
       <c r="T80">
-        <v>2.060683718236184</v>
+        <v>2.148822457253985</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.74810933815363</v>
+        <v>3.700664916151685</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07620274015023015</v>
+        <v>0.07598837138278308</v>
       </c>
       <c r="C81">
-        <v>287.9104675865659</v>
+        <v>286.7947272633979</v>
       </c>
       <c r="D81">
-        <v>643.6044675865659</v>
+        <v>648.1747272633978</v>
       </c>
       <c r="E81">
-        <v>140.794</v>
+        <v>146.48</v>
       </c>
       <c r="F81">
-        <v>449.194</v>
+        <v>454.8799999999999</v>
       </c>
       <c r="G81">
         <v>93.5</v>
@@ -7923,28 +7923,28 @@
         <v>101.9</v>
       </c>
       <c r="M81">
-        <v>27.5355922</v>
+        <v>27.884144</v>
       </c>
       <c r="N81">
-        <v>74.3644078</v>
+        <v>74.015856</v>
       </c>
       <c r="O81">
-        <v>25.283898652</v>
+        <v>25.16539104</v>
       </c>
       <c r="P81">
-        <v>49.08050914799999</v>
+        <v>48.85046496</v>
       </c>
       <c r="Q81">
-        <v>75.180509148</v>
+        <v>74.95046496000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2106710483344293</v>
+        <v>0.2181098569139154</v>
       </c>
       <c r="T81">
-        <v>2.148822457253985</v>
+        <v>2.245775070173566</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.700664916151685</v>
+        <v>3.65440660469979</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07598837138278308</v>
+        <v>0.07577400261533601</v>
       </c>
       <c r="C82">
-        <v>286.7947272633979</v>
+        <v>285.7443583186478</v>
       </c>
       <c r="D82">
-        <v>648.1747272633978</v>
+        <v>652.8103583186478</v>
       </c>
       <c r="E82">
-        <v>146.48</v>
+        <v>152.166</v>
       </c>
       <c r="F82">
-        <v>454.8799999999999</v>
+        <v>460.566</v>
       </c>
       <c r="G82">
         <v>93.5</v>
@@ -8005,28 +8005,28 @@
         <v>101.9</v>
       </c>
       <c r="M82">
-        <v>27.884144</v>
+        <v>28.2326958</v>
       </c>
       <c r="N82">
-        <v>74.015856</v>
+        <v>73.66730419999999</v>
       </c>
       <c r="O82">
-        <v>25.16539104</v>
+        <v>25.046883428</v>
       </c>
       <c r="P82">
-        <v>48.85046496</v>
+        <v>48.62042077199999</v>
       </c>
       <c r="Q82">
-        <v>74.95046496000001</v>
+        <v>74.720420772</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2181098569139154</v>
+        <v>0.2263316979754528</v>
       </c>
       <c r="T82">
-        <v>2.245775070173566</v>
+        <v>2.352933221295208</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.65440660469979</v>
+        <v>3.609290473777569</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07577400261533601</v>
+        <v>0.07555963384788895</v>
       </c>
       <c r="C83">
-        <v>285.7443583186478</v>
+        <v>284.7607734291538</v>
       </c>
       <c r="D83">
-        <v>652.8103583186478</v>
+        <v>657.5127734291538</v>
       </c>
       <c r="E83">
-        <v>152.166</v>
+        <v>157.852</v>
       </c>
       <c r="F83">
-        <v>460.566</v>
+        <v>466.252</v>
       </c>
       <c r="G83">
         <v>93.5</v>
@@ -8087,28 +8087,28 @@
         <v>101.9</v>
       </c>
       <c r="M83">
-        <v>28.2326958</v>
+        <v>28.5812476</v>
       </c>
       <c r="N83">
-        <v>73.66730419999999</v>
+        <v>73.31875239999999</v>
       </c>
       <c r="O83">
-        <v>25.046883428</v>
+        <v>24.928375816</v>
       </c>
       <c r="P83">
-        <v>48.62042077199999</v>
+        <v>48.39037658399999</v>
       </c>
       <c r="Q83">
-        <v>74.720420772</v>
+        <v>74.490376584</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2263316979754528</v>
+        <v>0.2354670769327165</v>
       </c>
       <c r="T83">
-        <v>2.352933221295208</v>
+        <v>2.471997833652588</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.609290473777569</v>
+        <v>3.565274736292477</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07555963384788895</v>
+        <v>0.07534526508044187</v>
       </c>
       <c r="C84">
-        <v>284.7607734291538</v>
+        <v>283.8454262710546</v>
       </c>
       <c r="D84">
-        <v>657.5127734291538</v>
+        <v>662.2834262710546</v>
       </c>
       <c r="E84">
-        <v>157.852</v>
+        <v>163.538</v>
       </c>
       <c r="F84">
-        <v>466.252</v>
+        <v>471.938</v>
       </c>
       <c r="G84">
         <v>93.5</v>
@@ -8169,28 +8169,28 @@
         <v>101.9</v>
       </c>
       <c r="M84">
-        <v>28.5812476</v>
+        <v>28.9297994</v>
       </c>
       <c r="N84">
-        <v>73.31875239999999</v>
+        <v>72.9702006</v>
       </c>
       <c r="O84">
-        <v>24.928375816</v>
+        <v>24.809868204</v>
       </c>
       <c r="P84">
-        <v>48.39037658399999</v>
+        <v>48.160332396</v>
       </c>
       <c r="Q84">
-        <v>74.490376584</v>
+        <v>74.26033239600001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2354670769327165</v>
+        <v>0.2456772063555406</v>
       </c>
       <c r="T84">
-        <v>2.471997833652588</v>
+        <v>2.605070047463778</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.565274736292477</v>
+        <v>3.522319618987749</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07534526508044187</v>
+        <v>0.07668321631299482</v>
       </c>
       <c r="C85">
-        <v>283.8454262710546</v>
+        <v>249.4673717422035</v>
       </c>
       <c r="D85">
-        <v>662.2834262710546</v>
+        <v>633.5913717422035</v>
       </c>
       <c r="E85">
-        <v>163.538</v>
+        <v>169.224</v>
       </c>
       <c r="F85">
-        <v>471.938</v>
+        <v>477.624</v>
       </c>
       <c r="G85">
         <v>93.5</v>
@@ -8251,45 +8251,45 @@
         <v>101.9</v>
       </c>
       <c r="M85">
-        <v>28.9297994</v>
+        <v>30.6156984</v>
       </c>
       <c r="N85">
-        <v>72.9702006</v>
+        <v>71.28430159999999</v>
       </c>
       <c r="O85">
-        <v>24.809868204</v>
+        <v>24.236662544</v>
       </c>
       <c r="P85">
-        <v>48.160332396</v>
+        <v>47.04763905599999</v>
       </c>
       <c r="Q85">
-        <v>74.26033239600001</v>
+        <v>73.147639056</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2456772063555406</v>
+        <v>0.2571636019562177</v>
       </c>
       <c r="T85">
-        <v>2.605070047463778</v>
+        <v>2.754776288001366</v>
       </c>
       <c r="U85">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V85">
         <v>0.34</v>
       </c>
       <c r="W85">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.522319618987749</v>
+        <v>3.328357846639879</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07668321631299482</v>
+        <v>0.07648732754554777</v>
       </c>
       <c r="C86">
-        <v>249.4673717422036</v>
+        <v>247.8258240553434</v>
       </c>
       <c r="D86">
-        <v>633.5913717422035</v>
+        <v>637.6358240553433</v>
       </c>
       <c r="E86">
-        <v>169.2239999999999</v>
+        <v>174.9099999999999</v>
       </c>
       <c r="F86">
-        <v>477.6239999999999</v>
+        <v>483.3099999999999</v>
       </c>
       <c r="G86">
         <v>93.5</v>
@@ -8333,28 +8333,28 @@
         <v>101.9</v>
       </c>
       <c r="M86">
-        <v>30.6156984</v>
+        <v>30.980171</v>
       </c>
       <c r="N86">
-        <v>71.28430159999999</v>
+        <v>70.91982899999999</v>
       </c>
       <c r="O86">
-        <v>24.236662544</v>
+        <v>24.11274186</v>
       </c>
       <c r="P86">
-        <v>47.04763905599999</v>
+        <v>46.80708713999999</v>
       </c>
       <c r="Q86">
-        <v>73.147639056</v>
+        <v>72.90708714</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2571636019562176</v>
+        <v>0.2701815169703184</v>
       </c>
       <c r="T86">
-        <v>2.754776288001365</v>
+        <v>2.924443360610632</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.32835784663988</v>
+        <v>3.28920069550294</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07648732754554777</v>
+        <v>0.0762914387781007</v>
       </c>
       <c r="C87">
-        <v>247.8258240553434</v>
+        <v>246.2362426128043</v>
       </c>
       <c r="D87">
-        <v>637.6358240553433</v>
+        <v>641.7322426128043</v>
       </c>
       <c r="E87">
-        <v>174.9099999999999</v>
+        <v>180.5959999999999</v>
       </c>
       <c r="F87">
-        <v>483.3099999999999</v>
+        <v>488.9959999999999</v>
       </c>
       <c r="G87">
         <v>93.5</v>
@@ -8415,28 +8415,28 @@
         <v>101.9</v>
       </c>
       <c r="M87">
-        <v>30.980171</v>
+        <v>31.3446436</v>
       </c>
       <c r="N87">
-        <v>70.91982899999999</v>
+        <v>70.55535639999999</v>
       </c>
       <c r="O87">
-        <v>24.11274186</v>
+        <v>23.988821176</v>
       </c>
       <c r="P87">
-        <v>46.80708713999999</v>
+        <v>46.56653522399999</v>
       </c>
       <c r="Q87">
-        <v>72.90708714</v>
+        <v>72.666535224</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2701815169703184</v>
+        <v>0.2850591341292907</v>
       </c>
       <c r="T87">
-        <v>2.924443360610632</v>
+        <v>3.118348586449793</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.28920069550294</v>
+        <v>3.250954175787789</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0762914387781007</v>
+        <v>0.07609555001065363</v>
       </c>
       <c r="C88">
-        <v>246.2362426128043</v>
+        <v>244.6996354441694</v>
       </c>
       <c r="D88">
-        <v>641.7322426128043</v>
+        <v>645.8816354441693</v>
       </c>
       <c r="E88">
-        <v>180.5959999999999</v>
+        <v>186.2819999999999</v>
       </c>
       <c r="F88">
-        <v>488.9959999999999</v>
+        <v>494.6819999999999</v>
       </c>
       <c r="G88">
         <v>93.5</v>
@@ -8497,28 +8497,28 @@
         <v>101.9</v>
       </c>
       <c r="M88">
-        <v>31.3446436</v>
+        <v>31.7091162</v>
       </c>
       <c r="N88">
-        <v>70.55535639999999</v>
+        <v>70.19088379999999</v>
       </c>
       <c r="O88">
-        <v>23.988821176</v>
+        <v>23.864900492</v>
       </c>
       <c r="P88">
-        <v>46.56653522399999</v>
+        <v>46.32598330799999</v>
       </c>
       <c r="Q88">
-        <v>72.666535224</v>
+        <v>72.425983308</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2850591341292907</v>
+        <v>0.3022256154665664</v>
       </c>
       <c r="T88">
-        <v>3.118348586449793</v>
+        <v>3.34208538549498</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.250954175787789</v>
+        <v>3.213586886410918</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07609555001065363</v>
+        <v>0.07589966124320657</v>
       </c>
       <c r="C89">
-        <v>244.6996354441694</v>
+        <v>243.2170368200702</v>
       </c>
       <c r="D89">
-        <v>645.8816354441693</v>
+        <v>650.0850368200702</v>
       </c>
       <c r="E89">
-        <v>186.2819999999999</v>
+        <v>191.968</v>
       </c>
       <c r="F89">
-        <v>494.6819999999999</v>
+        <v>500.3679999999999</v>
       </c>
       <c r="G89">
         <v>93.5</v>
@@ -8579,28 +8579,28 @@
         <v>101.9</v>
       </c>
       <c r="M89">
-        <v>31.7091162</v>
+        <v>32.0735888</v>
       </c>
       <c r="N89">
-        <v>70.19088379999999</v>
+        <v>69.8264112</v>
       </c>
       <c r="O89">
-        <v>23.864900492</v>
+        <v>23.740979808</v>
       </c>
       <c r="P89">
-        <v>46.32598330799999</v>
+        <v>46.085431392</v>
       </c>
       <c r="Q89">
-        <v>72.425983308</v>
+        <v>72.185431392</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3022256154665664</v>
+        <v>0.3222531770267215</v>
       </c>
       <c r="T89">
-        <v>3.34208538549498</v>
+        <v>3.603111651047699</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.213586886410918</v>
+        <v>3.177068853610794</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07589966124320657</v>
+        <v>0.0757037724757595</v>
       </c>
       <c r="C90">
-        <v>243.2170368200702</v>
+        <v>241.7895081116672</v>
       </c>
       <c r="D90">
-        <v>650.0850368200702</v>
+        <v>654.3435081116671</v>
       </c>
       <c r="E90">
-        <v>191.968</v>
+        <v>197.6539999999999</v>
       </c>
       <c r="F90">
-        <v>500.3679999999999</v>
+        <v>506.0539999999999</v>
       </c>
       <c r="G90">
         <v>93.5</v>
@@ -8661,28 +8661,28 @@
         <v>101.9</v>
       </c>
       <c r="M90">
-        <v>32.0735888</v>
+        <v>32.4380614</v>
       </c>
       <c r="N90">
-        <v>69.8264112</v>
+        <v>69.4619386</v>
       </c>
       <c r="O90">
-        <v>23.740979808</v>
+        <v>23.617059124</v>
       </c>
       <c r="P90">
-        <v>46.085431392</v>
+        <v>45.844879476</v>
       </c>
       <c r="Q90">
-        <v>72.185431392</v>
+        <v>71.94487947600001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3222531770267215</v>
+        <v>0.3459221134159955</v>
       </c>
       <c r="T90">
-        <v>3.603111651047699</v>
+        <v>3.911597237610001</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.177068853610794</v>
+        <v>3.141371450761234</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0757037724757595</v>
+        <v>0.07550788370831243</v>
       </c>
       <c r="C91">
-        <v>241.7895081116672</v>
+        <v>240.4181386841277</v>
       </c>
       <c r="D91">
-        <v>654.3435081116671</v>
+        <v>658.6581386841276</v>
       </c>
       <c r="E91">
-        <v>197.6539999999999</v>
+        <v>203.34</v>
       </c>
       <c r="F91">
-        <v>506.0539999999999</v>
+        <v>511.74</v>
       </c>
       <c r="G91">
         <v>93.5</v>
@@ -8743,28 +8743,28 @@
         <v>101.9</v>
       </c>
       <c r="M91">
-        <v>32.4380614</v>
+        <v>32.802534</v>
       </c>
       <c r="N91">
-        <v>69.4619386</v>
+        <v>69.097466</v>
       </c>
       <c r="O91">
-        <v>23.617059124</v>
+        <v>23.49313844</v>
       </c>
       <c r="P91">
-        <v>45.844879476</v>
+        <v>45.60432756</v>
       </c>
       <c r="Q91">
-        <v>71.94487947600001</v>
+        <v>71.70432756000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3459221134159955</v>
+        <v>0.3743248370831245</v>
       </c>
       <c r="T91">
-        <v>3.911597237610001</v>
+        <v>4.281779941484765</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.141371450761234</v>
+        <v>3.106467323530554</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07550788370831243</v>
+        <v>0.07531199494086538</v>
       </c>
       <c r="C92">
-        <v>240.4181386841277</v>
+        <v>239.104046825693</v>
       </c>
       <c r="D92">
-        <v>658.6581386841276</v>
+        <v>663.0300468256929</v>
       </c>
       <c r="E92">
-        <v>203.34</v>
+        <v>209.026</v>
       </c>
       <c r="F92">
-        <v>511.74</v>
+        <v>517.4259999999999</v>
       </c>
       <c r="G92">
         <v>93.5</v>
@@ -8825,28 +8825,28 @@
         <v>101.9</v>
       </c>
       <c r="M92">
-        <v>32.802534</v>
+        <v>33.1670066</v>
       </c>
       <c r="N92">
-        <v>69.097466</v>
+        <v>68.7329934</v>
       </c>
       <c r="O92">
-        <v>23.49313844</v>
+        <v>23.369217756</v>
       </c>
       <c r="P92">
-        <v>45.60432756</v>
+        <v>45.363775644</v>
       </c>
       <c r="Q92">
-        <v>71.70432756000001</v>
+        <v>71.46377564400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3743248370831245</v>
+        <v>0.4090392771207265</v>
       </c>
       <c r="T92">
-        <v>4.281779941484765</v>
+        <v>4.73422546844281</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.106467323530554</v>
+        <v>3.072330319975273</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07531199494086538</v>
+        <v>0.07511610617341832</v>
       </c>
       <c r="C93">
-        <v>239.104046825693</v>
+        <v>237.8483807139913</v>
       </c>
       <c r="D93">
-        <v>663.0300468256929</v>
+        <v>667.4603807139913</v>
       </c>
       <c r="E93">
-        <v>209.026</v>
+        <v>214.712</v>
       </c>
       <c r="F93">
-        <v>517.4259999999999</v>
+        <v>523.112</v>
       </c>
       <c r="G93">
         <v>93.5</v>
@@ -8907,28 +8907,28 @@
         <v>101.9</v>
       </c>
       <c r="M93">
-        <v>33.1670066</v>
+        <v>33.5314792</v>
       </c>
       <c r="N93">
-        <v>68.7329934</v>
+        <v>68.3685208</v>
       </c>
       <c r="O93">
-        <v>23.369217756</v>
+        <v>23.245297072</v>
       </c>
       <c r="P93">
-        <v>45.363775644</v>
+        <v>45.123223728</v>
       </c>
       <c r="Q93">
-        <v>71.46377564400001</v>
+        <v>71.22322372800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4090392771207265</v>
+        <v>0.4524323271677292</v>
       </c>
       <c r="T93">
-        <v>4.73422546844281</v>
+        <v>5.299782377140367</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.072330319975273</v>
+        <v>3.038935425192933</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07511610617341832</v>
+        <v>0.07492021740597124</v>
       </c>
       <c r="C94">
-        <v>237.8483807139913</v>
+        <v>236.652319421352</v>
       </c>
       <c r="D94">
-        <v>667.4603807139913</v>
+        <v>671.9503194213519</v>
       </c>
       <c r="E94">
-        <v>214.712</v>
+        <v>220.3979999999999</v>
       </c>
       <c r="F94">
-        <v>523.112</v>
+        <v>528.7979999999999</v>
       </c>
       <c r="G94">
         <v>93.5</v>
@@ -8989,28 +8989,28 @@
         <v>101.9</v>
       </c>
       <c r="M94">
-        <v>33.5314792</v>
+        <v>33.89595179999999</v>
       </c>
       <c r="N94">
-        <v>68.3685208</v>
+        <v>68.0040482</v>
       </c>
       <c r="O94">
-        <v>23.245297072</v>
+        <v>23.121376388</v>
       </c>
       <c r="P94">
-        <v>45.123223728</v>
+        <v>44.882671812</v>
       </c>
       <c r="Q94">
-        <v>71.22322372800001</v>
+        <v>70.98267181200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4524323271677292</v>
+        <v>0.5082233915138753</v>
       </c>
       <c r="T94">
-        <v>5.299782377140367</v>
+        <v>6.026926974037226</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.038935425192933</v>
+        <v>3.006258700190859</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07492021740597124</v>
+        <v>0.07956344863852419</v>
       </c>
       <c r="C95">
-        <v>236.652319421352</v>
+        <v>138.5580840167139</v>
       </c>
       <c r="D95">
-        <v>671.9503194213519</v>
+        <v>579.5420840167138</v>
       </c>
       <c r="E95">
-        <v>220.3979999999999</v>
+        <v>226.0839999999999</v>
       </c>
       <c r="F95">
-        <v>528.7979999999999</v>
+        <v>534.4839999999999</v>
       </c>
       <c r="G95">
         <v>93.5</v>
@@ -9071,45 +9071,45 @@
         <v>101.9</v>
       </c>
       <c r="M95">
-        <v>33.89595179999999</v>
+        <v>38.4293996</v>
       </c>
       <c r="N95">
-        <v>68.0040482</v>
+        <v>63.4706004</v>
       </c>
       <c r="O95">
-        <v>23.121376388</v>
+        <v>21.580004136</v>
       </c>
       <c r="P95">
-        <v>44.882671812</v>
+        <v>41.890596264</v>
       </c>
       <c r="Q95">
-        <v>70.98267181200001</v>
+        <v>67.990596264</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5082233915138753</v>
+        <v>0.5826114773087369</v>
       </c>
       <c r="T95">
-        <v>6.026926974037226</v>
+        <v>6.996453103233036</v>
       </c>
       <c r="U95">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V95">
         <v>0.34</v>
       </c>
       <c r="W95">
-        <v>0.042306</v>
+        <v>0.047454</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y95">
-        <v>3.006258700190859</v>
+        <v>2.651615717670489</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07956344863852419</v>
+        <v>0.07941903987107712</v>
       </c>
       <c r="C96">
-        <v>138.5580840167139</v>
+        <v>135.3614756934986</v>
       </c>
       <c r="D96">
-        <v>579.5420840167138</v>
+        <v>582.0314756934986</v>
       </c>
       <c r="E96">
-        <v>226.0839999999999</v>
+        <v>231.77</v>
       </c>
       <c r="F96">
-        <v>534.4839999999999</v>
+        <v>540.17</v>
       </c>
       <c r="G96">
         <v>93.5</v>
@@ -9153,28 +9153,28 @@
         <v>101.9</v>
       </c>
       <c r="M96">
-        <v>38.4293996</v>
+        <v>38.838223</v>
       </c>
       <c r="N96">
-        <v>63.4706004</v>
+        <v>63.06177699999999</v>
       </c>
       <c r="O96">
-        <v>21.580004136</v>
+        <v>21.44100418</v>
       </c>
       <c r="P96">
-        <v>41.890596264</v>
+        <v>41.62077281999999</v>
       </c>
       <c r="Q96">
-        <v>67.990596264</v>
+        <v>67.72077282000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5826114773087369</v>
+        <v>0.6867547974215433</v>
       </c>
       <c r="T96">
-        <v>6.996453103233036</v>
+        <v>8.353789684107175</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.651615717670489</v>
+        <v>2.623703973273957</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07941903987107712</v>
+        <v>0.07927463110363006</v>
       </c>
       <c r="C97">
-        <v>135.3614756934986</v>
+        <v>132.1863457240031</v>
       </c>
       <c r="D97">
-        <v>582.0314756934986</v>
+        <v>584.5423457240031</v>
       </c>
       <c r="E97">
-        <v>231.77</v>
+        <v>237.456</v>
       </c>
       <c r="F97">
-        <v>540.17</v>
+        <v>545.856</v>
       </c>
       <c r="G97">
         <v>93.5</v>
@@ -9235,28 +9235,28 @@
         <v>101.9</v>
       </c>
       <c r="M97">
-        <v>38.838223</v>
+        <v>39.2470464</v>
       </c>
       <c r="N97">
-        <v>63.06177699999999</v>
+        <v>62.65295359999999</v>
       </c>
       <c r="O97">
-        <v>21.44100418</v>
+        <v>21.302004224</v>
       </c>
       <c r="P97">
-        <v>41.62077281999999</v>
+        <v>41.35094937599999</v>
       </c>
       <c r="Q97">
-        <v>67.72077282000001</v>
+        <v>67.450949376</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6867547974215433</v>
+        <v>0.842969777590753</v>
       </c>
       <c r="T97">
-        <v>8.353789684107175</v>
+        <v>10.38979455541838</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.623703973273957</v>
+        <v>2.596373723552353</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07927463110363006</v>
+        <v>0.079130222336183</v>
       </c>
       <c r="C98">
-        <v>132.1863457240032</v>
+        <v>129.0329732839152</v>
       </c>
       <c r="D98">
-        <v>584.5423457240031</v>
+        <v>587.0749732839151</v>
       </c>
       <c r="E98">
-        <v>237.4559999999999</v>
+        <v>243.1419999999999</v>
       </c>
       <c r="F98">
-        <v>545.8559999999999</v>
+        <v>551.5419999999999</v>
       </c>
       <c r="G98">
         <v>93.5</v>
@@ -9317,28 +9317,28 @@
         <v>101.9</v>
       </c>
       <c r="M98">
-        <v>39.2470464</v>
+        <v>39.6558698</v>
       </c>
       <c r="N98">
-        <v>62.6529536</v>
+        <v>62.24413019999999</v>
       </c>
       <c r="O98">
-        <v>21.302004224</v>
+        <v>21.163004268</v>
       </c>
       <c r="P98">
-        <v>41.350949376</v>
+        <v>41.08112593199999</v>
       </c>
       <c r="Q98">
-        <v>67.45094937600001</v>
+        <v>67.181125932</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8429697775907508</v>
+        <v>1.103328077872766</v>
       </c>
       <c r="T98">
-        <v>10.38979455541835</v>
+        <v>13.78313600760368</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.596373723552354</v>
+        <v>2.569606984134288</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.079130222336183</v>
+        <v>0.07898581356873594</v>
       </c>
       <c r="C99">
-        <v>129.0329732839152</v>
+        <v>125.9016424082791</v>
       </c>
       <c r="D99">
-        <v>587.0749732839151</v>
+        <v>589.6296424082791</v>
       </c>
       <c r="E99">
-        <v>243.1419999999999</v>
+        <v>248.828</v>
       </c>
       <c r="F99">
-        <v>551.5419999999999</v>
+        <v>557.228</v>
       </c>
       <c r="G99">
         <v>93.5</v>
@@ -9399,28 +9399,28 @@
         <v>101.9</v>
       </c>
       <c r="M99">
-        <v>39.6558698</v>
+        <v>40.0646932</v>
       </c>
       <c r="N99">
-        <v>62.24413019999999</v>
+        <v>61.83530679999999</v>
       </c>
       <c r="O99">
-        <v>21.163004268</v>
+        <v>21.024004312</v>
       </c>
       <c r="P99">
-        <v>41.08112593199999</v>
+        <v>40.811302488</v>
       </c>
       <c r="Q99">
-        <v>67.181125932</v>
+        <v>66.911302488</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.103328077872766</v>
+        <v>1.624044678436795</v>
       </c>
       <c r="T99">
-        <v>13.78313600760368</v>
+        <v>20.56981891197434</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.569606984134288</v>
+        <v>2.543386504704346</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07898581356873594</v>
+        <v>0.07884140480128887</v>
       </c>
       <c r="C100">
-        <v>125.9016424082791</v>
+        <v>122.7926420976844</v>
       </c>
       <c r="D100">
-        <v>589.6296424082791</v>
+        <v>592.2066420976843</v>
       </c>
       <c r="E100">
-        <v>248.828</v>
+        <v>254.5139999999999</v>
       </c>
       <c r="F100">
-        <v>557.228</v>
+        <v>562.9139999999999</v>
       </c>
       <c r="G100">
         <v>93.5</v>
@@ -9481,28 +9481,28 @@
         <v>101.9</v>
       </c>
       <c r="M100">
-        <v>40.0646932</v>
+        <v>40.4735166</v>
       </c>
       <c r="N100">
-        <v>61.83530679999999</v>
+        <v>61.4264834</v>
       </c>
       <c r="O100">
-        <v>21.024004312</v>
+        <v>20.885004356</v>
       </c>
       <c r="P100">
-        <v>40.811302488</v>
+        <v>40.541479044</v>
       </c>
       <c r="Q100">
-        <v>66.911302488</v>
+        <v>66.64147904400001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.624044678436795</v>
+        <v>3.186194480128884</v>
       </c>
       <c r="T100">
-        <v>20.56981891197434</v>
+        <v>40.92986762508632</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.543386504704346</v>
+        <v>2.517695731929555</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07884140480128887</v>
-      </c>
-      <c r="C101">
-        <v>122.7926420976844</v>
-      </c>
-      <c r="D101">
-        <v>592.2066420976843</v>
-      </c>
-      <c r="E101">
-        <v>254.5139999999999</v>
-      </c>
-      <c r="F101">
-        <v>562.9139999999999</v>
-      </c>
-      <c r="G101">
-        <v>93.5</v>
-      </c>
-      <c r="H101">
-        <v>260.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>128</v>
-      </c>
-      <c r="K101">
-        <v>26.10000000000001</v>
-      </c>
-      <c r="L101">
-        <v>101.9</v>
-      </c>
-      <c r="M101">
-        <v>40.4735166</v>
-      </c>
-      <c r="N101">
-        <v>61.4264834</v>
-      </c>
-      <c r="O101">
-        <v>20.885004356</v>
-      </c>
-      <c r="P101">
-        <v>40.541479044</v>
-      </c>
-      <c r="Q101">
-        <v>66.64147904400001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.186194480128884</v>
-      </c>
-      <c r="T101">
-        <v>40.92986762508632</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.34</v>
-      </c>
-      <c r="W101">
-        <v>0.047454</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.517695731929555</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
